--- a/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44233,6 +44233,4214 @@
         <v>198</v>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>632gURJ8</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>45497.875</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F239" t="n">
+        <v>20931</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" t="n">
+        <v>4</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Mqp3HsDl</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>8v74vG3f</t>
+        </is>
+      </c>
+      <c r="K239" t="n">
+        <v>49</v>
+      </c>
+      <c r="L239" t="n">
+        <v>51</v>
+      </c>
+      <c r="M239" t="n">
+        <v>9</v>
+      </c>
+      <c r="N239" t="n">
+        <v>12</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1</v>
+      </c>
+      <c r="P239" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>9</v>
+      </c>
+      <c r="R239" t="n">
+        <v>5</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>C4noIxvE</t>
+        </is>
+      </c>
+      <c r="U239" t="n">
+        <v>167</v>
+      </c>
+      <c r="V239" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W239" t="n">
+        <v>0</v>
+      </c>
+      <c r="X239" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y239" t="inlineStr"/>
+      <c r="Z239" t="inlineStr"/>
+      <c r="AA239" t="inlineStr"/>
+      <c r="AB239" t="inlineStr"/>
+      <c r="AC239" t="inlineStr"/>
+      <c r="AD239" t="inlineStr"/>
+      <c r="AE239" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>177.8181818181818</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>1.818181818181818</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>76.09090909090909</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>8718181.818181818</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>77.09090909090909</v>
+      </c>
+      <c r="AK239" t="inlineStr"/>
+      <c r="AL239" t="inlineStr"/>
+      <c r="AM239" t="inlineStr"/>
+      <c r="AN239" t="inlineStr"/>
+      <c r="AO239" t="inlineStr"/>
+      <c r="AP239" t="inlineStr"/>
+      <c r="AQ239" t="n">
+        <v>27.34722222222222</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>180.0138888888889</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>1.486111111111111</v>
+      </c>
+      <c r="AT239" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AU239" t="n">
+        <v>6499652.777777778</v>
+      </c>
+      <c r="AV239" t="n">
+        <v>75.94444444444444</v>
+      </c>
+      <c r="AW239" t="inlineStr"/>
+      <c r="AX239" t="inlineStr"/>
+      <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr"/>
+      <c r="BA239" t="inlineStr"/>
+      <c r="BB239" t="inlineStr"/>
+      <c r="BC239" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="BE239" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF239" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG239" t="n">
+        <v>166</v>
+      </c>
+      <c r="BH239" t="n">
+        <v>48500000</v>
+      </c>
+      <c r="BI239" t="n">
+        <v>166</v>
+      </c>
+      <c r="BJ239" t="inlineStr"/>
+      <c r="BK239" t="inlineStr"/>
+      <c r="BL239" t="inlineStr"/>
+      <c r="BM239" t="inlineStr"/>
+      <c r="BN239" t="inlineStr"/>
+      <c r="BO239" t="inlineStr"/>
+      <c r="BP239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>IcKcrkcE</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>45511.83333333334</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stevis b 
+  usa </t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyworth stadium
+  hamtramck  mi </t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>7933</v>
+      </c>
+      <c r="F240" t="n">
+        <v>7166</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="K240" t="n">
+        <v>54</v>
+      </c>
+      <c r="L240" t="n">
+        <v>46</v>
+      </c>
+      <c r="M240" t="n">
+        <v>7</v>
+      </c>
+      <c r="N240" t="n">
+        <v>9</v>
+      </c>
+      <c r="O240" t="n">
+        <v>2</v>
+      </c>
+      <c r="P240" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>12</v>
+      </c>
+      <c r="R240" t="n">
+        <v>17</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="U240" t="n">
+        <v>167</v>
+      </c>
+      <c r="V240" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W240" t="n">
+        <v>0</v>
+      </c>
+      <c r="X240" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA240" t="inlineStr"/>
+      <c r="AB240" t="inlineStr"/>
+      <c r="AC240" t="inlineStr"/>
+      <c r="AD240" t="inlineStr"/>
+      <c r="AE240" t="inlineStr"/>
+      <c r="AF240" t="inlineStr"/>
+      <c r="AG240" t="inlineStr"/>
+      <c r="AH240" t="inlineStr"/>
+      <c r="AI240" t="inlineStr"/>
+      <c r="AJ240" t="inlineStr"/>
+      <c r="AK240" t="inlineStr"/>
+      <c r="AL240" t="inlineStr"/>
+      <c r="AM240" t="inlineStr"/>
+      <c r="AN240" t="inlineStr"/>
+      <c r="AO240" t="inlineStr"/>
+      <c r="AP240" t="inlineStr"/>
+      <c r="AQ240" t="inlineStr"/>
+      <c r="AR240" t="inlineStr"/>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AU240" t="inlineStr"/>
+      <c r="AV240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr"/>
+      <c r="AX240" t="inlineStr"/>
+      <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr"/>
+      <c r="BA240" t="inlineStr"/>
+      <c r="BB240" t="inlineStr"/>
+      <c r="BC240" t="inlineStr"/>
+      <c r="BD240" t="inlineStr"/>
+      <c r="BE240" t="inlineStr"/>
+      <c r="BF240" t="inlineStr"/>
+      <c r="BG240" t="inlineStr"/>
+      <c r="BH240" t="inlineStr"/>
+      <c r="BI240" t="inlineStr"/>
+      <c r="BJ240" t="inlineStr"/>
+      <c r="BK240" t="inlineStr"/>
+      <c r="BL240" t="inlineStr"/>
+      <c r="BM240" t="inlineStr"/>
+      <c r="BN240" t="inlineStr"/>
+      <c r="BO240" t="inlineStr"/>
+      <c r="BP240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>CKJ1s9CK</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>45511.83333333334</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michael a  carroll stadium
+  indianapolis  in </t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>12111</v>
+      </c>
+      <c r="F241" t="n">
+        <v>8091</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="K241" t="n">
+        <v>43</v>
+      </c>
+      <c r="L241" t="n">
+        <v>57</v>
+      </c>
+      <c r="M241" t="n">
+        <v>18</v>
+      </c>
+      <c r="N241" t="n">
+        <v>11</v>
+      </c>
+      <c r="O241" t="n">
+        <v>6</v>
+      </c>
+      <c r="P241" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>27</v>
+      </c>
+      <c r="R241" t="n">
+        <v>14</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="U241" t="n">
+        <v>167</v>
+      </c>
+      <c r="V241" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W241" t="n">
+        <v>0</v>
+      </c>
+      <c r="X241" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA241" t="inlineStr"/>
+      <c r="AB241" t="inlineStr"/>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
+      <c r="AE241" t="inlineStr"/>
+      <c r="AF241" t="inlineStr"/>
+      <c r="AG241" t="inlineStr"/>
+      <c r="AH241" t="inlineStr"/>
+      <c r="AI241" t="inlineStr"/>
+      <c r="AJ241" t="inlineStr"/>
+      <c r="AK241" t="inlineStr"/>
+      <c r="AL241" t="inlineStr"/>
+      <c r="AM241" t="inlineStr"/>
+      <c r="AN241" t="inlineStr"/>
+      <c r="AO241" t="inlineStr"/>
+      <c r="AP241" t="inlineStr"/>
+      <c r="AQ241" t="inlineStr"/>
+      <c r="AR241" t="inlineStr"/>
+      <c r="AS241" t="inlineStr"/>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AU241" t="inlineStr"/>
+      <c r="AV241" t="inlineStr"/>
+      <c r="AW241" t="n">
+        <v>23.71428571428572</v>
+      </c>
+      <c r="AX241" t="n">
+        <v>178.8571428571429</v>
+      </c>
+      <c r="AY241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ241" t="n">
+        <v>57.14285714285715</v>
+      </c>
+      <c r="BA241" t="n">
+        <v>264285.7142857143</v>
+      </c>
+      <c r="BB241" t="n">
+        <v>63.14285714285715</v>
+      </c>
+      <c r="BC241" t="inlineStr"/>
+      <c r="BD241" t="inlineStr"/>
+      <c r="BE241" t="inlineStr"/>
+      <c r="BF241" t="inlineStr"/>
+      <c r="BG241" t="inlineStr"/>
+      <c r="BH241" t="inlineStr"/>
+      <c r="BI241" t="inlineStr"/>
+      <c r="BJ241" t="inlineStr"/>
+      <c r="BK241" t="inlineStr"/>
+      <c r="BL241" t="inlineStr"/>
+      <c r="BM241" t="inlineStr"/>
+      <c r="BN241" t="inlineStr"/>
+      <c r="BO241" t="inlineStr"/>
+      <c r="BP241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>E5m1wufk</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>45507.95833333334</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bensalah n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardinale stadium
+  seaside  ca </t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F242" t="n">
+        <v>4024</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H242" t="n">
+        <v>2</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K242" t="n">
+        <v>45</v>
+      </c>
+      <c r="L242" t="n">
+        <v>55</v>
+      </c>
+      <c r="M242" t="n">
+        <v>14</v>
+      </c>
+      <c r="N242" t="n">
+        <v>14</v>
+      </c>
+      <c r="O242" t="n">
+        <v>4</v>
+      </c>
+      <c r="P242" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>14</v>
+      </c>
+      <c r="R242" t="n">
+        <v>11</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="U242" t="n">
+        <v>167</v>
+      </c>
+      <c r="V242" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W242" t="n">
+        <v>0</v>
+      </c>
+      <c r="X242" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA242" t="inlineStr"/>
+      <c r="AB242" t="inlineStr"/>
+      <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
+      <c r="AE242" t="inlineStr"/>
+      <c r="AF242" t="inlineStr"/>
+      <c r="AG242" t="inlineStr"/>
+      <c r="AH242" t="inlineStr"/>
+      <c r="AI242" t="inlineStr"/>
+      <c r="AJ242" t="inlineStr"/>
+      <c r="AK242" t="inlineStr"/>
+      <c r="AL242" t="inlineStr"/>
+      <c r="AM242" t="inlineStr"/>
+      <c r="AN242" t="inlineStr"/>
+      <c r="AO242" t="inlineStr"/>
+      <c r="AP242" t="inlineStr"/>
+      <c r="AQ242" t="inlineStr"/>
+      <c r="AR242" t="inlineStr"/>
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AU242" t="inlineStr"/>
+      <c r="AV242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr"/>
+      <c r="AX242" t="inlineStr"/>
+      <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr"/>
+      <c r="BA242" t="inlineStr"/>
+      <c r="BB242" t="inlineStr"/>
+      <c r="BC242" t="inlineStr"/>
+      <c r="BD242" t="inlineStr"/>
+      <c r="BE242" t="inlineStr"/>
+      <c r="BF242" t="inlineStr"/>
+      <c r="BG242" t="inlineStr"/>
+      <c r="BH242" t="inlineStr"/>
+      <c r="BI242" t="inlineStr"/>
+      <c r="BJ242" t="inlineStr"/>
+      <c r="BK242" t="inlineStr"/>
+      <c r="BL242" t="inlineStr"/>
+      <c r="BM242" t="inlineStr"/>
+      <c r="BN242" t="inlineStr"/>
+      <c r="BO242" t="inlineStr"/>
+      <c r="BP242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>MVj9yJO1</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>45507.95833333334</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">meyer b 
+  usa </t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">championship soccer stadium
+  irvine  ca </t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F243" t="n">
+        <v>3353</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="K243" t="n">
+        <v>49</v>
+      </c>
+      <c r="L243" t="n">
+        <v>51</v>
+      </c>
+      <c r="M243" t="n">
+        <v>7</v>
+      </c>
+      <c r="N243" t="n">
+        <v>13</v>
+      </c>
+      <c r="O243" t="n">
+        <v>1</v>
+      </c>
+      <c r="P243" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>11</v>
+      </c>
+      <c r="R243" t="n">
+        <v>10</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="U243" t="n">
+        <v>167</v>
+      </c>
+      <c r="V243" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W243" t="n">
+        <v>0</v>
+      </c>
+      <c r="X243" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA243" t="inlineStr"/>
+      <c r="AB243" t="inlineStr"/>
+      <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr"/>
+      <c r="AE243" t="inlineStr"/>
+      <c r="AF243" t="inlineStr"/>
+      <c r="AG243" t="inlineStr"/>
+      <c r="AH243" t="inlineStr"/>
+      <c r="AI243" t="inlineStr"/>
+      <c r="AJ243" t="inlineStr"/>
+      <c r="AK243" t="inlineStr"/>
+      <c r="AL243" t="inlineStr"/>
+      <c r="AM243" t="inlineStr"/>
+      <c r="AN243" t="inlineStr"/>
+      <c r="AO243" t="inlineStr"/>
+      <c r="AP243" t="inlineStr"/>
+      <c r="AQ243" t="inlineStr"/>
+      <c r="AR243" t="inlineStr"/>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AU243" t="inlineStr"/>
+      <c r="AV243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr"/>
+      <c r="AX243" t="inlineStr"/>
+      <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr"/>
+      <c r="BA243" t="inlineStr"/>
+      <c r="BB243" t="inlineStr"/>
+      <c r="BC243" t="inlineStr"/>
+      <c r="BD243" t="inlineStr"/>
+      <c r="BE243" t="inlineStr"/>
+      <c r="BF243" t="inlineStr"/>
+      <c r="BG243" t="inlineStr"/>
+      <c r="BH243" t="inlineStr"/>
+      <c r="BI243" t="inlineStr"/>
+      <c r="BJ243" t="inlineStr"/>
+      <c r="BK243" t="inlineStr"/>
+      <c r="BL243" t="inlineStr"/>
+      <c r="BM243" t="inlineStr"/>
+      <c r="BN243" t="inlineStr"/>
+      <c r="BO243" t="inlineStr"/>
+      <c r="BP243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>0MkDzwv8</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>45507.95833333334</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F244" t="n">
+        <v>9459</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="K244" t="n">
+        <v>63</v>
+      </c>
+      <c r="L244" t="n">
+        <v>37</v>
+      </c>
+      <c r="M244" t="n">
+        <v>16</v>
+      </c>
+      <c r="N244" t="n">
+        <v>15</v>
+      </c>
+      <c r="O244" t="n">
+        <v>8</v>
+      </c>
+      <c r="P244" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>9</v>
+      </c>
+      <c r="R244" t="n">
+        <v>15</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="U244" t="n">
+        <v>167</v>
+      </c>
+      <c r="V244" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W244" t="n">
+        <v>0</v>
+      </c>
+      <c r="X244" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA244" t="inlineStr"/>
+      <c r="AB244" t="inlineStr"/>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
+      <c r="AE244" t="inlineStr"/>
+      <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="inlineStr"/>
+      <c r="AH244" t="inlineStr"/>
+      <c r="AI244" t="inlineStr"/>
+      <c r="AJ244" t="inlineStr"/>
+      <c r="AK244" t="inlineStr"/>
+      <c r="AL244" t="inlineStr"/>
+      <c r="AM244" t="inlineStr"/>
+      <c r="AN244" t="inlineStr"/>
+      <c r="AO244" t="inlineStr"/>
+      <c r="AP244" t="inlineStr"/>
+      <c r="AQ244" t="inlineStr"/>
+      <c r="AR244" t="inlineStr"/>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AU244" t="inlineStr"/>
+      <c r="AV244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr"/>
+      <c r="AX244" t="inlineStr"/>
+      <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr"/>
+      <c r="BA244" t="inlineStr"/>
+      <c r="BB244" t="inlineStr"/>
+      <c r="BC244" t="inlineStr"/>
+      <c r="BD244" t="inlineStr"/>
+      <c r="BE244" t="inlineStr"/>
+      <c r="BF244" t="inlineStr"/>
+      <c r="BG244" t="inlineStr"/>
+      <c r="BH244" t="inlineStr"/>
+      <c r="BI244" t="inlineStr"/>
+      <c r="BJ244" t="inlineStr"/>
+      <c r="BK244" t="inlineStr"/>
+      <c r="BL244" t="inlineStr"/>
+      <c r="BM244" t="inlineStr"/>
+      <c r="BN244" t="inlineStr"/>
+      <c r="BO244" t="inlineStr"/>
+      <c r="BP244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>rHDMpN1F</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>45507.91666666666</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F245" t="n">
+        <v>8023</v>
+      </c>
+      <c r="G245" t="n">
+        <v>2</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="K245" t="n">
+        <v>56</v>
+      </c>
+      <c r="L245" t="n">
+        <v>44</v>
+      </c>
+      <c r="M245" t="n">
+        <v>21</v>
+      </c>
+      <c r="N245" t="n">
+        <v>5</v>
+      </c>
+      <c r="O245" t="n">
+        <v>7</v>
+      </c>
+      <c r="P245" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>8</v>
+      </c>
+      <c r="R245" t="n">
+        <v>12</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="U245" t="n">
+        <v>167</v>
+      </c>
+      <c r="V245" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W245" t="n">
+        <v>0</v>
+      </c>
+      <c r="X245" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA245" t="inlineStr"/>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
+      <c r="AE245" t="inlineStr"/>
+      <c r="AF245" t="inlineStr"/>
+      <c r="AG245" t="inlineStr"/>
+      <c r="AH245" t="inlineStr"/>
+      <c r="AI245" t="inlineStr"/>
+      <c r="AJ245" t="inlineStr"/>
+      <c r="AK245" t="inlineStr"/>
+      <c r="AL245" t="inlineStr"/>
+      <c r="AM245" t="inlineStr"/>
+      <c r="AN245" t="inlineStr"/>
+      <c r="AO245" t="inlineStr"/>
+      <c r="AP245" t="inlineStr"/>
+      <c r="AQ245" t="inlineStr"/>
+      <c r="AR245" t="inlineStr"/>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AU245" t="inlineStr"/>
+      <c r="AV245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr"/>
+      <c r="AX245" t="inlineStr"/>
+      <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr"/>
+      <c r="BA245" t="inlineStr"/>
+      <c r="BB245" t="inlineStr"/>
+      <c r="BC245" t="inlineStr"/>
+      <c r="BD245" t="inlineStr"/>
+      <c r="BE245" t="inlineStr"/>
+      <c r="BF245" t="inlineStr"/>
+      <c r="BG245" t="inlineStr"/>
+      <c r="BH245" t="inlineStr"/>
+      <c r="BI245" t="inlineStr"/>
+      <c r="BJ245" t="inlineStr"/>
+      <c r="BK245" t="inlineStr"/>
+      <c r="BL245" t="inlineStr"/>
+      <c r="BM245" t="inlineStr"/>
+      <c r="BN245" t="inlineStr"/>
+      <c r="BO245" t="inlineStr"/>
+      <c r="BP245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>S8i5xa9e</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>45507.91666666666</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stevis b 
+  usa </t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F246" t="n">
+        <v>9376</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="K246" t="n">
+        <v>65</v>
+      </c>
+      <c r="L246" t="n">
+        <v>35</v>
+      </c>
+      <c r="M246" t="n">
+        <v>8</v>
+      </c>
+      <c r="N246" t="n">
+        <v>12</v>
+      </c>
+      <c r="O246" t="n">
+        <v>4</v>
+      </c>
+      <c r="P246" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>14</v>
+      </c>
+      <c r="R246" t="n">
+        <v>18</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="U246" t="n">
+        <v>167</v>
+      </c>
+      <c r="V246" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W246" t="n">
+        <v>0</v>
+      </c>
+      <c r="X246" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA246" t="inlineStr"/>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
+      <c r="AE246" t="inlineStr"/>
+      <c r="AF246" t="inlineStr"/>
+      <c r="AG246" t="inlineStr"/>
+      <c r="AH246" t="inlineStr"/>
+      <c r="AI246" t="inlineStr"/>
+      <c r="AJ246" t="inlineStr"/>
+      <c r="AK246" t="inlineStr"/>
+      <c r="AL246" t="inlineStr"/>
+      <c r="AM246" t="inlineStr"/>
+      <c r="AN246" t="inlineStr"/>
+      <c r="AO246" t="inlineStr"/>
+      <c r="AP246" t="inlineStr"/>
+      <c r="AQ246" t="inlineStr"/>
+      <c r="AR246" t="inlineStr"/>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AU246" t="inlineStr"/>
+      <c r="AV246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr"/>
+      <c r="AX246" t="inlineStr"/>
+      <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr"/>
+      <c r="BA246" t="inlineStr"/>
+      <c r="BB246" t="inlineStr"/>
+      <c r="BC246" t="inlineStr"/>
+      <c r="BD246" t="inlineStr"/>
+      <c r="BE246" t="inlineStr"/>
+      <c r="BF246" t="inlineStr"/>
+      <c r="BG246" t="inlineStr"/>
+      <c r="BH246" t="inlineStr"/>
+      <c r="BI246" t="inlineStr"/>
+      <c r="BJ246" t="inlineStr"/>
+      <c r="BK246" t="inlineStr"/>
+      <c r="BL246" t="inlineStr"/>
+      <c r="BM246" t="inlineStr"/>
+      <c r="BN246" t="inlineStr"/>
+      <c r="BO246" t="inlineStr"/>
+      <c r="BP246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>v7LgqVs8</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>45507.91666666666</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">griggs j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota field
+  san antonio  tx </t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>8296</v>
+      </c>
+      <c r="F247" t="n">
+        <v>6356</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="K247" t="n">
+        <v>51</v>
+      </c>
+      <c r="L247" t="n">
+        <v>49</v>
+      </c>
+      <c r="M247" t="n">
+        <v>12</v>
+      </c>
+      <c r="N247" t="n">
+        <v>8</v>
+      </c>
+      <c r="O247" t="n">
+        <v>3</v>
+      </c>
+      <c r="P247" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>16</v>
+      </c>
+      <c r="R247" t="n">
+        <v>12</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="U247" t="n">
+        <v>167</v>
+      </c>
+      <c r="V247" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W247" t="n">
+        <v>0</v>
+      </c>
+      <c r="X247" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr"/>
+      <c r="AE247" t="inlineStr"/>
+      <c r="AF247" t="inlineStr"/>
+      <c r="AG247" t="inlineStr"/>
+      <c r="AH247" t="inlineStr"/>
+      <c r="AI247" t="inlineStr"/>
+      <c r="AJ247" t="inlineStr"/>
+      <c r="AK247" t="inlineStr"/>
+      <c r="AL247" t="inlineStr"/>
+      <c r="AM247" t="inlineStr"/>
+      <c r="AN247" t="inlineStr"/>
+      <c r="AO247" t="inlineStr"/>
+      <c r="AP247" t="inlineStr"/>
+      <c r="AQ247" t="n">
+        <v>23.09090909090909</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>180.7272727272727</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>57.72727272727273</v>
+      </c>
+      <c r="AU247" t="n">
+        <v>370000</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>64.45454545454545</v>
+      </c>
+      <c r="AW247" t="inlineStr"/>
+      <c r="AX247" t="inlineStr"/>
+      <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr"/>
+      <c r="BA247" t="inlineStr"/>
+      <c r="BB247" t="inlineStr"/>
+      <c r="BC247" t="inlineStr"/>
+      <c r="BD247" t="inlineStr"/>
+      <c r="BE247" t="inlineStr"/>
+      <c r="BF247" t="inlineStr"/>
+      <c r="BG247" t="inlineStr"/>
+      <c r="BH247" t="inlineStr"/>
+      <c r="BI247" t="inlineStr"/>
+      <c r="BJ247" t="inlineStr"/>
+      <c r="BK247" t="inlineStr"/>
+      <c r="BL247" t="inlineStr"/>
+      <c r="BM247" t="inlineStr"/>
+      <c r="BN247" t="inlineStr"/>
+      <c r="BO247" t="inlineStr"/>
+      <c r="BP247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>WtbdvLvq</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>45507.89583333334</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snyder t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">autozone park
+  memphis  tn </t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F248" t="n">
+        <v>2714</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="K248" t="n">
+        <v>51</v>
+      </c>
+      <c r="L248" t="n">
+        <v>49</v>
+      </c>
+      <c r="M248" t="n">
+        <v>19</v>
+      </c>
+      <c r="N248" t="n">
+        <v>11</v>
+      </c>
+      <c r="O248" t="n">
+        <v>6</v>
+      </c>
+      <c r="P248" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>11</v>
+      </c>
+      <c r="R248" t="n">
+        <v>14</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="U248" t="n">
+        <v>167</v>
+      </c>
+      <c r="V248" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W248" t="n">
+        <v>0</v>
+      </c>
+      <c r="X248" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA248" t="inlineStr"/>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr"/>
+      <c r="AE248" t="inlineStr"/>
+      <c r="AF248" t="inlineStr"/>
+      <c r="AG248" t="inlineStr"/>
+      <c r="AH248" t="inlineStr"/>
+      <c r="AI248" t="inlineStr"/>
+      <c r="AJ248" t="inlineStr"/>
+      <c r="AK248" t="inlineStr"/>
+      <c r="AL248" t="inlineStr"/>
+      <c r="AM248" t="inlineStr"/>
+      <c r="AN248" t="inlineStr"/>
+      <c r="AO248" t="inlineStr"/>
+      <c r="AP248" t="inlineStr"/>
+      <c r="AQ248" t="inlineStr"/>
+      <c r="AR248" t="inlineStr"/>
+      <c r="AS248" t="inlineStr"/>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AU248" t="inlineStr"/>
+      <c r="AV248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr"/>
+      <c r="AX248" t="inlineStr"/>
+      <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr"/>
+      <c r="BA248" t="inlineStr"/>
+      <c r="BB248" t="inlineStr"/>
+      <c r="BC248" t="inlineStr"/>
+      <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
+      <c r="BI248" t="inlineStr"/>
+      <c r="BJ248" t="inlineStr"/>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="inlineStr"/>
+      <c r="BM248" t="inlineStr"/>
+      <c r="BN248" t="inlineStr"/>
+      <c r="BO248" t="inlineStr"/>
+      <c r="BP248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>nkKDnqX2</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>45507.85416666666</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corbyn m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F249" t="n">
+        <v>4017</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>47</v>
+      </c>
+      <c r="L249" t="n">
+        <v>53</v>
+      </c>
+      <c r="M249" t="n">
+        <v>12</v>
+      </c>
+      <c r="N249" t="n">
+        <v>12</v>
+      </c>
+      <c r="O249" t="n">
+        <v>3</v>
+      </c>
+      <c r="P249" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>12</v>
+      </c>
+      <c r="R249" t="n">
+        <v>9</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="U249" t="n">
+        <v>167</v>
+      </c>
+      <c r="V249" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W249" t="n">
+        <v>0</v>
+      </c>
+      <c r="X249" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA249" t="inlineStr"/>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
+      <c r="AE249" t="inlineStr"/>
+      <c r="AF249" t="inlineStr"/>
+      <c r="AG249" t="inlineStr"/>
+      <c r="AH249" t="inlineStr"/>
+      <c r="AI249" t="inlineStr"/>
+      <c r="AJ249" t="inlineStr"/>
+      <c r="AK249" t="inlineStr"/>
+      <c r="AL249" t="inlineStr"/>
+      <c r="AM249" t="inlineStr"/>
+      <c r="AN249" t="inlineStr"/>
+      <c r="AO249" t="inlineStr"/>
+      <c r="AP249" t="inlineStr"/>
+      <c r="AQ249" t="inlineStr"/>
+      <c r="AR249" t="inlineStr"/>
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AU249" t="inlineStr"/>
+      <c r="AV249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr"/>
+      <c r="AX249" t="inlineStr"/>
+      <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr"/>
+      <c r="BA249" t="inlineStr"/>
+      <c r="BB249" t="inlineStr"/>
+      <c r="BC249" t="inlineStr"/>
+      <c r="BD249" t="inlineStr"/>
+      <c r="BE249" t="inlineStr"/>
+      <c r="BF249" t="inlineStr"/>
+      <c r="BG249" t="inlineStr"/>
+      <c r="BH249" t="inlineStr"/>
+      <c r="BI249" t="inlineStr"/>
+      <c r="BJ249" t="inlineStr"/>
+      <c r="BK249" t="inlineStr"/>
+      <c r="BL249" t="inlineStr"/>
+      <c r="BM249" t="inlineStr"/>
+      <c r="BN249" t="inlineStr"/>
+      <c r="BO249" t="inlineStr"/>
+      <c r="BP249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>UXBUr1WR</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>45507.85416666666</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jensen b 
+  usa </t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segra field
+  leesburg  va </t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1876</v>
+      </c>
+      <c r="G250" t="n">
+        <v>4</v>
+      </c>
+      <c r="H250" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="K250" t="n">
+        <v>73</v>
+      </c>
+      <c r="L250" t="n">
+        <v>27</v>
+      </c>
+      <c r="M250" t="n">
+        <v>21</v>
+      </c>
+      <c r="N250" t="n">
+        <v>5</v>
+      </c>
+      <c r="O250" t="n">
+        <v>7</v>
+      </c>
+      <c r="P250" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>9</v>
+      </c>
+      <c r="R250" t="n">
+        <v>13</v>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="U250" t="n">
+        <v>167</v>
+      </c>
+      <c r="V250" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W250" t="n">
+        <v>0</v>
+      </c>
+      <c r="X250" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA250" t="inlineStr"/>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+      <c r="AE250" t="inlineStr"/>
+      <c r="AF250" t="inlineStr"/>
+      <c r="AG250" t="inlineStr"/>
+      <c r="AH250" t="inlineStr"/>
+      <c r="AI250" t="inlineStr"/>
+      <c r="AJ250" t="inlineStr"/>
+      <c r="AK250" t="inlineStr"/>
+      <c r="AL250" t="inlineStr"/>
+      <c r="AM250" t="inlineStr"/>
+      <c r="AN250" t="inlineStr"/>
+      <c r="AO250" t="inlineStr"/>
+      <c r="AP250" t="inlineStr"/>
+      <c r="AQ250" t="inlineStr"/>
+      <c r="AR250" t="inlineStr"/>
+      <c r="AS250" t="inlineStr"/>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AU250" t="inlineStr"/>
+      <c r="AV250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr"/>
+      <c r="AX250" t="inlineStr"/>
+      <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr"/>
+      <c r="BA250" t="inlineStr"/>
+      <c r="BB250" t="inlineStr"/>
+      <c r="BC250" t="inlineStr"/>
+      <c r="BD250" t="inlineStr"/>
+      <c r="BE250" t="inlineStr"/>
+      <c r="BF250" t="inlineStr"/>
+      <c r="BG250" t="inlineStr"/>
+      <c r="BH250" t="inlineStr"/>
+      <c r="BI250" t="inlineStr"/>
+      <c r="BJ250" t="inlineStr"/>
+      <c r="BK250" t="inlineStr"/>
+      <c r="BL250" t="inlineStr"/>
+      <c r="BM250" t="inlineStr"/>
+      <c r="BN250" t="inlineStr"/>
+      <c r="BO250" t="inlineStr"/>
+      <c r="BP250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>M7CQqsHL</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>45507.70833333334</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyworth stadium
+  hamtramck  mi </t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>7933</v>
+      </c>
+      <c r="F251" t="n">
+        <v>6862</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="K251" t="n">
+        <v>48</v>
+      </c>
+      <c r="L251" t="n">
+        <v>52</v>
+      </c>
+      <c r="M251" t="n">
+        <v>11</v>
+      </c>
+      <c r="N251" t="n">
+        <v>14</v>
+      </c>
+      <c r="O251" t="n">
+        <v>2</v>
+      </c>
+      <c r="P251" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>15</v>
+      </c>
+      <c r="R251" t="n">
+        <v>17</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="U251" t="n">
+        <v>167</v>
+      </c>
+      <c r="V251" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W251" t="n">
+        <v>0</v>
+      </c>
+      <c r="X251" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA251" t="inlineStr"/>
+      <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
+      <c r="AE251" t="inlineStr"/>
+      <c r="AF251" t="inlineStr"/>
+      <c r="AG251" t="inlineStr"/>
+      <c r="AH251" t="inlineStr"/>
+      <c r="AI251" t="inlineStr"/>
+      <c r="AJ251" t="inlineStr"/>
+      <c r="AK251" t="inlineStr"/>
+      <c r="AL251" t="inlineStr"/>
+      <c r="AM251" t="inlineStr"/>
+      <c r="AN251" t="inlineStr"/>
+      <c r="AO251" t="inlineStr"/>
+      <c r="AP251" t="inlineStr"/>
+      <c r="AQ251" t="inlineStr"/>
+      <c r="AR251" t="inlineStr"/>
+      <c r="AS251" t="inlineStr"/>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AU251" t="inlineStr"/>
+      <c r="AV251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr"/>
+      <c r="AX251" t="inlineStr"/>
+      <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr"/>
+      <c r="BA251" t="inlineStr"/>
+      <c r="BB251" t="inlineStr"/>
+      <c r="BC251" t="inlineStr"/>
+      <c r="BD251" t="inlineStr"/>
+      <c r="BE251" t="inlineStr"/>
+      <c r="BF251" t="inlineStr"/>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
+      <c r="BI251" t="inlineStr"/>
+      <c r="BJ251" t="inlineStr"/>
+      <c r="BK251" t="inlineStr"/>
+      <c r="BL251" t="inlineStr"/>
+      <c r="BM251" t="inlineStr"/>
+      <c r="BN251" t="inlineStr"/>
+      <c r="BO251" t="inlineStr"/>
+      <c r="BP251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>0hOHo3n9</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>45506.85416666666</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">encarnacion j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriots point soccer complex
+  mount pleasant  sc </t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F252" t="n">
+        <v>2845</v>
+      </c>
+      <c r="G252" t="n">
+        <v>5</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>62</v>
+      </c>
+      <c r="L252" t="n">
+        <v>38</v>
+      </c>
+      <c r="M252" t="n">
+        <v>18</v>
+      </c>
+      <c r="N252" t="n">
+        <v>8</v>
+      </c>
+      <c r="O252" t="n">
+        <v>10</v>
+      </c>
+      <c r="P252" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>9</v>
+      </c>
+      <c r="R252" t="n">
+        <v>16</v>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="U252" t="n">
+        <v>167</v>
+      </c>
+      <c r="V252" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W252" t="n">
+        <v>0</v>
+      </c>
+      <c r="X252" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA252" t="inlineStr"/>
+      <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+      <c r="AE252" t="inlineStr"/>
+      <c r="AF252" t="inlineStr"/>
+      <c r="AG252" t="inlineStr"/>
+      <c r="AH252" t="inlineStr"/>
+      <c r="AI252" t="inlineStr"/>
+      <c r="AJ252" t="inlineStr"/>
+      <c r="AK252" t="inlineStr"/>
+      <c r="AL252" t="inlineStr"/>
+      <c r="AM252" t="inlineStr"/>
+      <c r="AN252" t="inlineStr"/>
+      <c r="AO252" t="inlineStr"/>
+      <c r="AP252" t="inlineStr"/>
+      <c r="AQ252" t="inlineStr"/>
+      <c r="AR252" t="inlineStr"/>
+      <c r="AS252" t="inlineStr"/>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AU252" t="inlineStr"/>
+      <c r="AV252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr"/>
+      <c r="AX252" t="inlineStr"/>
+      <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr"/>
+      <c r="BA252" t="inlineStr"/>
+      <c r="BB252" t="inlineStr"/>
+      <c r="BC252" t="inlineStr"/>
+      <c r="BD252" t="inlineStr"/>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr"/>
+      <c r="BH252" t="inlineStr"/>
+      <c r="BI252" t="inlineStr"/>
+      <c r="BJ252" t="inlineStr"/>
+      <c r="BK252" t="inlineStr"/>
+      <c r="BL252" t="inlineStr"/>
+      <c r="BM252" t="inlineStr"/>
+      <c r="BN252" t="inlineStr"/>
+      <c r="BO252" t="inlineStr"/>
+      <c r="BP252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>YoWVNaf2</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>45504.91666666666</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmanovic e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F253" t="n">
+        <v>7558</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="K253" t="n">
+        <v>58</v>
+      </c>
+      <c r="L253" t="n">
+        <v>42</v>
+      </c>
+      <c r="M253" t="n">
+        <v>8</v>
+      </c>
+      <c r="N253" t="n">
+        <v>12</v>
+      </c>
+      <c r="O253" t="n">
+        <v>3</v>
+      </c>
+      <c r="P253" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>13</v>
+      </c>
+      <c r="R253" t="n">
+        <v>12</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="U253" t="n">
+        <v>167</v>
+      </c>
+      <c r="V253" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W253" t="n">
+        <v>0</v>
+      </c>
+      <c r="X253" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA253" t="inlineStr"/>
+      <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr"/>
+      <c r="AE253" t="inlineStr"/>
+      <c r="AF253" t="inlineStr"/>
+      <c r="AG253" t="inlineStr"/>
+      <c r="AH253" t="inlineStr"/>
+      <c r="AI253" t="inlineStr"/>
+      <c r="AJ253" t="inlineStr"/>
+      <c r="AK253" t="inlineStr"/>
+      <c r="AL253" t="inlineStr"/>
+      <c r="AM253" t="inlineStr"/>
+      <c r="AN253" t="inlineStr"/>
+      <c r="AO253" t="inlineStr"/>
+      <c r="AP253" t="inlineStr"/>
+      <c r="AQ253" t="inlineStr"/>
+      <c r="AR253" t="inlineStr"/>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AU253" t="inlineStr"/>
+      <c r="AV253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr"/>
+      <c r="AX253" t="inlineStr"/>
+      <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr"/>
+      <c r="BA253" t="inlineStr"/>
+      <c r="BB253" t="inlineStr"/>
+      <c r="BC253" t="inlineStr"/>
+      <c r="BD253" t="inlineStr"/>
+      <c r="BE253" t="inlineStr"/>
+      <c r="BF253" t="inlineStr"/>
+      <c r="BG253" t="inlineStr"/>
+      <c r="BH253" t="inlineStr"/>
+      <c r="BI253" t="inlineStr"/>
+      <c r="BJ253" t="inlineStr"/>
+      <c r="BK253" t="inlineStr"/>
+      <c r="BL253" t="inlineStr"/>
+      <c r="BM253" t="inlineStr"/>
+      <c r="BN253" t="inlineStr"/>
+      <c r="BO253" t="inlineStr"/>
+      <c r="BP253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>feXROuud</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>45504.85416666666</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corrigan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trinity health stadium
+  east hartford  ct </t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="K254" t="n">
+        <v>39</v>
+      </c>
+      <c r="L254" t="n">
+        <v>61</v>
+      </c>
+      <c r="M254" t="n">
+        <v>7</v>
+      </c>
+      <c r="N254" t="n">
+        <v>11</v>
+      </c>
+      <c r="O254" t="n">
+        <v>4</v>
+      </c>
+      <c r="P254" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>16</v>
+      </c>
+      <c r="R254" t="n">
+        <v>13</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="U254" t="n">
+        <v>167</v>
+      </c>
+      <c r="V254" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W254" t="n">
+        <v>0</v>
+      </c>
+      <c r="X254" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
+      <c r="AE254" t="inlineStr"/>
+      <c r="AF254" t="inlineStr"/>
+      <c r="AG254" t="inlineStr"/>
+      <c r="AH254" t="inlineStr"/>
+      <c r="AI254" t="inlineStr"/>
+      <c r="AJ254" t="inlineStr"/>
+      <c r="AK254" t="inlineStr"/>
+      <c r="AL254" t="inlineStr"/>
+      <c r="AM254" t="inlineStr"/>
+      <c r="AN254" t="inlineStr"/>
+      <c r="AO254" t="inlineStr"/>
+      <c r="AP254" t="inlineStr"/>
+      <c r="AQ254" t="inlineStr"/>
+      <c r="AR254" t="inlineStr"/>
+      <c r="AS254" t="inlineStr"/>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AU254" t="inlineStr"/>
+      <c r="AV254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr"/>
+      <c r="AX254" t="inlineStr"/>
+      <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr"/>
+      <c r="BA254" t="inlineStr"/>
+      <c r="BB254" t="inlineStr"/>
+      <c r="BC254" t="inlineStr"/>
+      <c r="BD254" t="inlineStr"/>
+      <c r="BE254" t="inlineStr"/>
+      <c r="BF254" t="inlineStr"/>
+      <c r="BG254" t="inlineStr"/>
+      <c r="BH254" t="inlineStr"/>
+      <c r="BI254" t="inlineStr"/>
+      <c r="BJ254" t="inlineStr"/>
+      <c r="BK254" t="inlineStr"/>
+      <c r="BL254" t="inlineStr"/>
+      <c r="BM254" t="inlineStr"/>
+      <c r="BN254" t="inlineStr"/>
+      <c r="BO254" t="inlineStr"/>
+      <c r="BP254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>hEuyZP23</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>45500.91666666666</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">southwest university park
+  el paso  tx </t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F255" t="n">
+        <v>5577</v>
+      </c>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>47</v>
+      </c>
+      <c r="L255" t="n">
+        <v>53</v>
+      </c>
+      <c r="M255" t="n">
+        <v>7</v>
+      </c>
+      <c r="N255" t="n">
+        <v>16</v>
+      </c>
+      <c r="O255" t="n">
+        <v>1</v>
+      </c>
+      <c r="P255" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>11</v>
+      </c>
+      <c r="R255" t="n">
+        <v>16</v>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="U255" t="n">
+        <v>167</v>
+      </c>
+      <c r="V255" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W255" t="n">
+        <v>0</v>
+      </c>
+      <c r="X255" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA255" t="inlineStr"/>
+      <c r="AB255" t="inlineStr"/>
+      <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
+      <c r="AE255" t="inlineStr"/>
+      <c r="AF255" t="inlineStr"/>
+      <c r="AG255" t="inlineStr"/>
+      <c r="AH255" t="inlineStr"/>
+      <c r="AI255" t="inlineStr"/>
+      <c r="AJ255" t="inlineStr"/>
+      <c r="AK255" t="inlineStr"/>
+      <c r="AL255" t="inlineStr"/>
+      <c r="AM255" t="inlineStr"/>
+      <c r="AN255" t="inlineStr"/>
+      <c r="AO255" t="inlineStr"/>
+      <c r="AP255" t="inlineStr"/>
+      <c r="AQ255" t="inlineStr"/>
+      <c r="AR255" t="inlineStr"/>
+      <c r="AS255" t="inlineStr"/>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AU255" t="inlineStr"/>
+      <c r="AV255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr"/>
+      <c r="AX255" t="inlineStr"/>
+      <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr"/>
+      <c r="BA255" t="inlineStr"/>
+      <c r="BB255" t="inlineStr"/>
+      <c r="BC255" t="inlineStr"/>
+      <c r="BD255" t="inlineStr"/>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
+      <c r="BG255" t="inlineStr"/>
+      <c r="BH255" t="inlineStr"/>
+      <c r="BI255" t="inlineStr"/>
+      <c r="BJ255" t="inlineStr"/>
+      <c r="BK255" t="inlineStr"/>
+      <c r="BL255" t="inlineStr"/>
+      <c r="BM255" t="inlineStr"/>
+      <c r="BN255" t="inlineStr"/>
+      <c r="BO255" t="inlineStr"/>
+      <c r="BP255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>0vqqX3XF</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>45500.89583333334</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">autozone park
+  memphis  tn </t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F256" t="n">
+        <v>3594</v>
+      </c>
+      <c r="G256" t="n">
+        <v>1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>46</v>
+      </c>
+      <c r="L256" t="n">
+        <v>54</v>
+      </c>
+      <c r="M256" t="n">
+        <v>8</v>
+      </c>
+      <c r="N256" t="n">
+        <v>8</v>
+      </c>
+      <c r="O256" t="n">
+        <v>1</v>
+      </c>
+      <c r="P256" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>23</v>
+      </c>
+      <c r="R256" t="n">
+        <v>18</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="U256" t="n">
+        <v>167</v>
+      </c>
+      <c r="V256" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W256" t="n">
+        <v>0</v>
+      </c>
+      <c r="X256" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA256" t="inlineStr"/>
+      <c r="AB256" t="inlineStr"/>
+      <c r="AC256" t="inlineStr"/>
+      <c r="AD256" t="inlineStr"/>
+      <c r="AE256" t="inlineStr"/>
+      <c r="AF256" t="inlineStr"/>
+      <c r="AG256" t="inlineStr"/>
+      <c r="AH256" t="inlineStr"/>
+      <c r="AI256" t="inlineStr"/>
+      <c r="AJ256" t="inlineStr"/>
+      <c r="AK256" t="inlineStr"/>
+      <c r="AL256" t="inlineStr"/>
+      <c r="AM256" t="inlineStr"/>
+      <c r="AN256" t="inlineStr"/>
+      <c r="AO256" t="inlineStr"/>
+      <c r="AP256" t="inlineStr"/>
+      <c r="AQ256" t="inlineStr"/>
+      <c r="AR256" t="inlineStr"/>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AU256" t="inlineStr"/>
+      <c r="AV256" t="inlineStr"/>
+      <c r="AW256" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AY256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>60.16666666666666</v>
+      </c>
+      <c r="BA256" t="n">
+        <v>490000</v>
+      </c>
+      <c r="BB256" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="BC256" t="inlineStr"/>
+      <c r="BD256" t="inlineStr"/>
+      <c r="BE256" t="inlineStr"/>
+      <c r="BF256" t="inlineStr"/>
+      <c r="BG256" t="inlineStr"/>
+      <c r="BH256" t="inlineStr"/>
+      <c r="BI256" t="inlineStr"/>
+      <c r="BJ256" t="inlineStr"/>
+      <c r="BK256" t="inlineStr"/>
+      <c r="BL256" t="inlineStr"/>
+      <c r="BM256" t="inlineStr"/>
+      <c r="BN256" t="inlineStr"/>
+      <c r="BO256" t="inlineStr"/>
+      <c r="BP256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>MmpuYqI9</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>45500.875</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corrigan m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lynn family stadium
+  louisville  ky </t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>15304</v>
+      </c>
+      <c r="F257" t="n">
+        <v>9701</v>
+      </c>
+      <c r="G257" t="n">
+        <v>4</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>52</v>
+      </c>
+      <c r="L257" t="n">
+        <v>48</v>
+      </c>
+      <c r="M257" t="n">
+        <v>23</v>
+      </c>
+      <c r="N257" t="n">
+        <v>7</v>
+      </c>
+      <c r="O257" t="n">
+        <v>6</v>
+      </c>
+      <c r="P257" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>7</v>
+      </c>
+      <c r="R257" t="n">
+        <v>10</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="U257" t="n">
+        <v>167</v>
+      </c>
+      <c r="V257" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W257" t="n">
+        <v>0</v>
+      </c>
+      <c r="X257" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA257" t="inlineStr"/>
+      <c r="AB257" t="inlineStr"/>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
+      <c r="AE257" t="inlineStr"/>
+      <c r="AF257" t="inlineStr"/>
+      <c r="AG257" t="inlineStr"/>
+      <c r="AH257" t="inlineStr"/>
+      <c r="AI257" t="inlineStr"/>
+      <c r="AJ257" t="inlineStr"/>
+      <c r="AK257" t="inlineStr"/>
+      <c r="AL257" t="inlineStr"/>
+      <c r="AM257" t="inlineStr"/>
+      <c r="AN257" t="inlineStr"/>
+      <c r="AO257" t="inlineStr"/>
+      <c r="AP257" t="inlineStr"/>
+      <c r="AQ257" t="inlineStr"/>
+      <c r="AR257" t="inlineStr"/>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AU257" t="inlineStr"/>
+      <c r="AV257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr"/>
+      <c r="AX257" t="inlineStr"/>
+      <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr"/>
+      <c r="BA257" t="inlineStr"/>
+      <c r="BB257" t="inlineStr"/>
+      <c r="BC257" t="inlineStr"/>
+      <c r="BD257" t="inlineStr"/>
+      <c r="BE257" t="inlineStr"/>
+      <c r="BF257" t="inlineStr"/>
+      <c r="BG257" t="inlineStr"/>
+      <c r="BH257" t="inlineStr"/>
+      <c r="BI257" t="inlineStr"/>
+      <c r="BJ257" t="inlineStr"/>
+      <c r="BK257" t="inlineStr"/>
+      <c r="BL257" t="inlineStr"/>
+      <c r="BM257" t="inlineStr"/>
+      <c r="BN257" t="inlineStr"/>
+      <c r="BO257" t="inlineStr"/>
+      <c r="BP257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>CI2lBMAd</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>45500.85416666666</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thompson m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="n">
+        <v>3</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="K258" t="n">
+        <v>43</v>
+      </c>
+      <c r="L258" t="n">
+        <v>57</v>
+      </c>
+      <c r="M258" t="n">
+        <v>24</v>
+      </c>
+      <c r="N258" t="n">
+        <v>12</v>
+      </c>
+      <c r="O258" t="n">
+        <v>11</v>
+      </c>
+      <c r="P258" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>11</v>
+      </c>
+      <c r="R258" t="n">
+        <v>14</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="U258" t="n">
+        <v>167</v>
+      </c>
+      <c r="V258" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W258" t="n">
+        <v>0</v>
+      </c>
+      <c r="X258" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA258" t="inlineStr"/>
+      <c r="AB258" t="inlineStr"/>
+      <c r="AC258" t="inlineStr"/>
+      <c r="AD258" t="inlineStr"/>
+      <c r="AE258" t="inlineStr"/>
+      <c r="AF258" t="inlineStr"/>
+      <c r="AG258" t="inlineStr"/>
+      <c r="AH258" t="inlineStr"/>
+      <c r="AI258" t="inlineStr"/>
+      <c r="AJ258" t="inlineStr"/>
+      <c r="AK258" t="inlineStr"/>
+      <c r="AL258" t="inlineStr"/>
+      <c r="AM258" t="inlineStr"/>
+      <c r="AN258" t="inlineStr"/>
+      <c r="AO258" t="inlineStr"/>
+      <c r="AP258" t="inlineStr"/>
+      <c r="AQ258" t="inlineStr"/>
+      <c r="AR258" t="inlineStr"/>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AU258" t="inlineStr"/>
+      <c r="AV258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr"/>
+      <c r="AX258" t="inlineStr"/>
+      <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr"/>
+      <c r="BA258" t="inlineStr"/>
+      <c r="BB258" t="inlineStr"/>
+      <c r="BC258" t="inlineStr"/>
+      <c r="BD258" t="inlineStr"/>
+      <c r="BE258" t="inlineStr"/>
+      <c r="BF258" t="inlineStr"/>
+      <c r="BG258" t="inlineStr"/>
+      <c r="BH258" t="inlineStr"/>
+      <c r="BI258" t="inlineStr"/>
+      <c r="BJ258" t="inlineStr"/>
+      <c r="BK258" t="inlineStr"/>
+      <c r="BL258" t="inlineStr"/>
+      <c r="BM258" t="inlineStr"/>
+      <c r="BN258" t="inlineStr"/>
+      <c r="BO258" t="inlineStr"/>
+      <c r="BP258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>bTwJQ1Aq</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>45500.85416666666</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tattersall e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beirne stadium
+  pawtucket  ri </t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>5252</v>
+      </c>
+      <c r="F259" t="n">
+        <v>4045</v>
+      </c>
+      <c r="G259" t="n">
+        <v>2</v>
+      </c>
+      <c r="H259" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="K259" t="n">
+        <v>57</v>
+      </c>
+      <c r="L259" t="n">
+        <v>43</v>
+      </c>
+      <c r="M259" t="n">
+        <v>14</v>
+      </c>
+      <c r="N259" t="n">
+        <v>7</v>
+      </c>
+      <c r="O259" t="n">
+        <v>5</v>
+      </c>
+      <c r="P259" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>10</v>
+      </c>
+      <c r="R259" t="n">
+        <v>6</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="U259" t="n">
+        <v>167</v>
+      </c>
+      <c r="V259" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W259" t="n">
+        <v>0</v>
+      </c>
+      <c r="X259" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA259" t="inlineStr"/>
+      <c r="AB259" t="inlineStr"/>
+      <c r="AC259" t="inlineStr"/>
+      <c r="AD259" t="inlineStr"/>
+      <c r="AE259" t="inlineStr"/>
+      <c r="AF259" t="inlineStr"/>
+      <c r="AG259" t="inlineStr"/>
+      <c r="AH259" t="inlineStr"/>
+      <c r="AI259" t="inlineStr"/>
+      <c r="AJ259" t="inlineStr"/>
+      <c r="AK259" t="inlineStr"/>
+      <c r="AL259" t="inlineStr"/>
+      <c r="AM259" t="inlineStr"/>
+      <c r="AN259" t="inlineStr"/>
+      <c r="AO259" t="inlineStr"/>
+      <c r="AP259" t="inlineStr"/>
+      <c r="AQ259" t="inlineStr"/>
+      <c r="AR259" t="inlineStr"/>
+      <c r="AS259" t="inlineStr"/>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AU259" t="inlineStr"/>
+      <c r="AV259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr"/>
+      <c r="AX259" t="inlineStr"/>
+      <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr"/>
+      <c r="BA259" t="inlineStr"/>
+      <c r="BB259" t="inlineStr"/>
+      <c r="BC259" t="inlineStr"/>
+      <c r="BD259" t="inlineStr"/>
+      <c r="BE259" t="inlineStr"/>
+      <c r="BF259" t="inlineStr"/>
+      <c r="BG259" t="inlineStr"/>
+      <c r="BH259" t="inlineStr"/>
+      <c r="BI259" t="inlineStr"/>
+      <c r="BJ259" t="inlineStr"/>
+      <c r="BK259" t="inlineStr"/>
+      <c r="BL259" t="inlineStr"/>
+      <c r="BM259" t="inlineStr"/>
+      <c r="BN259" t="inlineStr"/>
+      <c r="BO259" t="inlineStr"/>
+      <c r="BP259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>xKxNPLPk</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>45500.85416666666</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">griggs j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">al lang stadium
+  st  petersburg  fl </t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>7227</v>
+      </c>
+      <c r="F260" t="n">
+        <v>5705</v>
+      </c>
+      <c r="G260" t="n">
+        <v>4</v>
+      </c>
+      <c r="H260" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="K260" t="n">
+        <v>43</v>
+      </c>
+      <c r="L260" t="n">
+        <v>57</v>
+      </c>
+      <c r="M260" t="n">
+        <v>12</v>
+      </c>
+      <c r="N260" t="n">
+        <v>16</v>
+      </c>
+      <c r="O260" t="n">
+        <v>6</v>
+      </c>
+      <c r="P260" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>23</v>
+      </c>
+      <c r="R260" t="n">
+        <v>16</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="U260" t="n">
+        <v>167</v>
+      </c>
+      <c r="V260" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W260" t="n">
+        <v>0</v>
+      </c>
+      <c r="X260" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA260" t="inlineStr"/>
+      <c r="AB260" t="inlineStr"/>
+      <c r="AC260" t="inlineStr"/>
+      <c r="AD260" t="inlineStr"/>
+      <c r="AE260" t="inlineStr"/>
+      <c r="AF260" t="inlineStr"/>
+      <c r="AG260" t="inlineStr"/>
+      <c r="AH260" t="inlineStr"/>
+      <c r="AI260" t="inlineStr"/>
+      <c r="AJ260" t="inlineStr"/>
+      <c r="AK260" t="inlineStr"/>
+      <c r="AL260" t="inlineStr"/>
+      <c r="AM260" t="inlineStr"/>
+      <c r="AN260" t="inlineStr"/>
+      <c r="AO260" t="inlineStr"/>
+      <c r="AP260" t="inlineStr"/>
+      <c r="AQ260" t="inlineStr"/>
+      <c r="AR260" t="inlineStr"/>
+      <c r="AS260" t="inlineStr"/>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AU260" t="inlineStr"/>
+      <c r="AV260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr"/>
+      <c r="AX260" t="inlineStr"/>
+      <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr"/>
+      <c r="BA260" t="inlineStr"/>
+      <c r="BB260" t="inlineStr"/>
+      <c r="BC260" t="inlineStr"/>
+      <c r="BD260" t="inlineStr"/>
+      <c r="BE260" t="inlineStr"/>
+      <c r="BF260" t="inlineStr"/>
+      <c r="BG260" t="inlineStr"/>
+      <c r="BH260" t="inlineStr"/>
+      <c r="BI260" t="inlineStr"/>
+      <c r="BJ260" t="inlineStr"/>
+      <c r="BK260" t="inlineStr"/>
+      <c r="BL260" t="inlineStr"/>
+      <c r="BM260" t="inlineStr"/>
+      <c r="BN260" t="inlineStr"/>
+      <c r="BO260" t="inlineStr"/>
+      <c r="BP260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>ENtXZ5mc</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>45500.83333333334</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">encarnacion j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyworth stadium
+  hamtramck  mi </t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>7933</v>
+      </c>
+      <c r="F261" t="n">
+        <v>6</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>45</v>
+      </c>
+      <c r="L261" t="n">
+        <v>55</v>
+      </c>
+      <c r="M261" t="n">
+        <v>12</v>
+      </c>
+      <c r="N261" t="n">
+        <v>17</v>
+      </c>
+      <c r="O261" t="n">
+        <v>5</v>
+      </c>
+      <c r="P261" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>15</v>
+      </c>
+      <c r="R261" t="n">
+        <v>16</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="U261" t="n">
+        <v>167</v>
+      </c>
+      <c r="V261" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W261" t="n">
+        <v>0</v>
+      </c>
+      <c r="X261" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA261" t="inlineStr"/>
+      <c r="AB261" t="inlineStr"/>
+      <c r="AC261" t="inlineStr"/>
+      <c r="AD261" t="inlineStr"/>
+      <c r="AE261" t="inlineStr"/>
+      <c r="AF261" t="inlineStr"/>
+      <c r="AG261" t="inlineStr"/>
+      <c r="AH261" t="inlineStr"/>
+      <c r="AI261" t="inlineStr"/>
+      <c r="AJ261" t="inlineStr"/>
+      <c r="AK261" t="inlineStr"/>
+      <c r="AL261" t="inlineStr"/>
+      <c r="AM261" t="inlineStr"/>
+      <c r="AN261" t="inlineStr"/>
+      <c r="AO261" t="inlineStr"/>
+      <c r="AP261" t="inlineStr"/>
+      <c r="AQ261" t="inlineStr"/>
+      <c r="AR261" t="inlineStr"/>
+      <c r="AS261" t="inlineStr"/>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AU261" t="inlineStr"/>
+      <c r="AV261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr"/>
+      <c r="AX261" t="inlineStr"/>
+      <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr"/>
+      <c r="BA261" t="inlineStr"/>
+      <c r="BB261" t="inlineStr"/>
+      <c r="BC261" t="inlineStr"/>
+      <c r="BD261" t="inlineStr"/>
+      <c r="BE261" t="inlineStr"/>
+      <c r="BF261" t="inlineStr"/>
+      <c r="BG261" t="inlineStr"/>
+      <c r="BH261" t="inlineStr"/>
+      <c r="BI261" t="inlineStr"/>
+      <c r="BJ261" t="inlineStr"/>
+      <c r="BK261" t="inlineStr"/>
+      <c r="BL261" t="inlineStr"/>
+      <c r="BM261" t="inlineStr"/>
+      <c r="BN261" t="inlineStr"/>
+      <c r="BO261" t="inlineStr"/>
+      <c r="BP261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>r3YmWNnM</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>45500.83333333334</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snyder t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riccardo silva stadium
+  miami  fl </t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1041</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>65</v>
+      </c>
+      <c r="L262" t="n">
+        <v>35</v>
+      </c>
+      <c r="M262" t="n">
+        <v>12</v>
+      </c>
+      <c r="N262" t="n">
+        <v>10</v>
+      </c>
+      <c r="O262" t="n">
+        <v>6</v>
+      </c>
+      <c r="P262" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>15</v>
+      </c>
+      <c r="R262" t="n">
+        <v>15</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="U262" t="n">
+        <v>167</v>
+      </c>
+      <c r="V262" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W262" t="n">
+        <v>0</v>
+      </c>
+      <c r="X262" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA262" t="inlineStr"/>
+      <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
+      <c r="AD262" t="inlineStr"/>
+      <c r="AE262" t="inlineStr"/>
+      <c r="AF262" t="inlineStr"/>
+      <c r="AG262" t="inlineStr"/>
+      <c r="AH262" t="inlineStr"/>
+      <c r="AI262" t="inlineStr"/>
+      <c r="AJ262" t="inlineStr"/>
+      <c r="AK262" t="inlineStr"/>
+      <c r="AL262" t="inlineStr"/>
+      <c r="AM262" t="inlineStr"/>
+      <c r="AN262" t="inlineStr"/>
+      <c r="AO262" t="inlineStr"/>
+      <c r="AP262" t="inlineStr"/>
+      <c r="AQ262" t="inlineStr"/>
+      <c r="AR262" t="inlineStr"/>
+      <c r="AS262" t="inlineStr"/>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AU262" t="inlineStr"/>
+      <c r="AV262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr"/>
+      <c r="AX262" t="inlineStr"/>
+      <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr"/>
+      <c r="BA262" t="inlineStr"/>
+      <c r="BB262" t="inlineStr"/>
+      <c r="BC262" t="inlineStr"/>
+      <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
+      <c r="BI262" t="inlineStr"/>
+      <c r="BJ262" t="inlineStr"/>
+      <c r="BK262" t="inlineStr"/>
+      <c r="BL262" t="inlineStr"/>
+      <c r="BM262" t="inlineStr"/>
+      <c r="BN262" t="inlineStr"/>
+      <c r="BO262" t="inlineStr"/>
+      <c r="BP262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>tliiVs2S</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>45500.83333333334</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">billeter a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F263" t="n">
+        <v>5613</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="K263" t="n">
+        <v>32</v>
+      </c>
+      <c r="L263" t="n">
+        <v>68</v>
+      </c>
+      <c r="M263" t="n">
+        <v>15</v>
+      </c>
+      <c r="N263" t="n">
+        <v>11</v>
+      </c>
+      <c r="O263" t="n">
+        <v>2</v>
+      </c>
+      <c r="P263" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>16</v>
+      </c>
+      <c r="R263" t="n">
+        <v>11</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="U263" t="n">
+        <v>167</v>
+      </c>
+      <c r="V263" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W263" t="n">
+        <v>0</v>
+      </c>
+      <c r="X263" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA263" t="inlineStr"/>
+      <c r="AB263" t="inlineStr"/>
+      <c r="AC263" t="inlineStr"/>
+      <c r="AD263" t="inlineStr"/>
+      <c r="AE263" t="inlineStr"/>
+      <c r="AF263" t="inlineStr"/>
+      <c r="AG263" t="inlineStr"/>
+      <c r="AH263" t="inlineStr"/>
+      <c r="AI263" t="inlineStr"/>
+      <c r="AJ263" t="inlineStr"/>
+      <c r="AK263" t="inlineStr"/>
+      <c r="AL263" t="inlineStr"/>
+      <c r="AM263" t="inlineStr"/>
+      <c r="AN263" t="inlineStr"/>
+      <c r="AO263" t="inlineStr"/>
+      <c r="AP263" t="inlineStr"/>
+      <c r="AQ263" t="inlineStr"/>
+      <c r="AR263" t="inlineStr"/>
+      <c r="AS263" t="inlineStr"/>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AU263" t="inlineStr"/>
+      <c r="AV263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr"/>
+      <c r="AX263" t="inlineStr"/>
+      <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr"/>
+      <c r="BA263" t="inlineStr"/>
+      <c r="BB263" t="inlineStr"/>
+      <c r="BC263" t="inlineStr"/>
+      <c r="BD263" t="inlineStr"/>
+      <c r="BE263" t="inlineStr"/>
+      <c r="BF263" t="inlineStr"/>
+      <c r="BG263" t="inlineStr"/>
+      <c r="BH263" t="inlineStr"/>
+      <c r="BI263" t="inlineStr"/>
+      <c r="BJ263" t="inlineStr"/>
+      <c r="BK263" t="inlineStr"/>
+      <c r="BL263" t="inlineStr"/>
+      <c r="BM263" t="inlineStr"/>
+      <c r="BN263" t="inlineStr"/>
+      <c r="BO263" t="inlineStr"/>
+      <c r="BP263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>SSyDUABH</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>45499.91666666666</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F264" t="n">
+        <v>8023</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="K264" t="n">
+        <v>49</v>
+      </c>
+      <c r="L264" t="n">
+        <v>51</v>
+      </c>
+      <c r="M264" t="n">
+        <v>22</v>
+      </c>
+      <c r="N264" t="n">
+        <v>5</v>
+      </c>
+      <c r="O264" t="n">
+        <v>9</v>
+      </c>
+      <c r="P264" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>21</v>
+      </c>
+      <c r="R264" t="n">
+        <v>11</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="U264" t="n">
+        <v>167</v>
+      </c>
+      <c r="V264" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W264" t="n">
+        <v>0</v>
+      </c>
+      <c r="X264" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA264" t="inlineStr"/>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr"/>
+      <c r="AD264" t="inlineStr"/>
+      <c r="AE264" t="inlineStr"/>
+      <c r="AF264" t="inlineStr"/>
+      <c r="AG264" t="inlineStr"/>
+      <c r="AH264" t="inlineStr"/>
+      <c r="AI264" t="inlineStr"/>
+      <c r="AJ264" t="inlineStr"/>
+      <c r="AK264" t="inlineStr"/>
+      <c r="AL264" t="inlineStr"/>
+      <c r="AM264" t="inlineStr"/>
+      <c r="AN264" t="inlineStr"/>
+      <c r="AO264" t="inlineStr"/>
+      <c r="AP264" t="inlineStr"/>
+      <c r="AQ264" t="inlineStr"/>
+      <c r="AR264" t="inlineStr"/>
+      <c r="AS264" t="inlineStr"/>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AU264" t="inlineStr"/>
+      <c r="AV264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr"/>
+      <c r="AX264" t="inlineStr"/>
+      <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr"/>
+      <c r="BA264" t="inlineStr"/>
+      <c r="BB264" t="inlineStr"/>
+      <c r="BC264" t="inlineStr"/>
+      <c r="BD264" t="inlineStr"/>
+      <c r="BE264" t="inlineStr"/>
+      <c r="BF264" t="inlineStr"/>
+      <c r="BG264" t="inlineStr"/>
+      <c r="BH264" t="inlineStr"/>
+      <c r="BI264" t="inlineStr"/>
+      <c r="BJ264" t="inlineStr"/>
+      <c r="BK264" t="inlineStr"/>
+      <c r="BL264" t="inlineStr"/>
+      <c r="BM264" t="inlineStr"/>
+      <c r="BN264" t="inlineStr"/>
+      <c r="BO264" t="inlineStr"/>
+      <c r="BP264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>4hatDrtp</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>45499.89583333334</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oneok field
+  tulsa  ok </t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>7833</v>
+      </c>
+      <c r="F265" t="n">
+        <v>3490</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="K265" t="n">
+        <v>58</v>
+      </c>
+      <c r="L265" t="n">
+        <v>42</v>
+      </c>
+      <c r="M265" t="n">
+        <v>12</v>
+      </c>
+      <c r="N265" t="n">
+        <v>8</v>
+      </c>
+      <c r="O265" t="n">
+        <v>1</v>
+      </c>
+      <c r="P265" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>14</v>
+      </c>
+      <c r="R265" t="n">
+        <v>18</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="U265" t="n">
+        <v>167</v>
+      </c>
+      <c r="V265" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W265" t="n">
+        <v>0</v>
+      </c>
+      <c r="X265" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA265" t="inlineStr"/>
+      <c r="AB265" t="inlineStr"/>
+      <c r="AC265" t="inlineStr"/>
+      <c r="AD265" t="inlineStr"/>
+      <c r="AE265" t="inlineStr"/>
+      <c r="AF265" t="inlineStr"/>
+      <c r="AG265" t="inlineStr"/>
+      <c r="AH265" t="inlineStr"/>
+      <c r="AI265" t="inlineStr"/>
+      <c r="AJ265" t="inlineStr"/>
+      <c r="AK265" t="inlineStr"/>
+      <c r="AL265" t="inlineStr"/>
+      <c r="AM265" t="inlineStr"/>
+      <c r="AN265" t="inlineStr"/>
+      <c r="AO265" t="inlineStr"/>
+      <c r="AP265" t="inlineStr"/>
+      <c r="AQ265" t="inlineStr"/>
+      <c r="AR265" t="inlineStr"/>
+      <c r="AS265" t="inlineStr"/>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AU265" t="inlineStr"/>
+      <c r="AV265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr"/>
+      <c r="AX265" t="inlineStr"/>
+      <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr"/>
+      <c r="BA265" t="inlineStr"/>
+      <c r="BB265" t="inlineStr"/>
+      <c r="BC265" t="inlineStr"/>
+      <c r="BD265" t="inlineStr"/>
+      <c r="BE265" t="inlineStr"/>
+      <c r="BF265" t="inlineStr"/>
+      <c r="BG265" t="inlineStr"/>
+      <c r="BH265" t="inlineStr"/>
+      <c r="BI265" t="inlineStr"/>
+      <c r="BJ265" t="inlineStr"/>
+      <c r="BK265" t="inlineStr"/>
+      <c r="BL265" t="inlineStr"/>
+      <c r="BM265" t="inlineStr"/>
+      <c r="BN265" t="inlineStr"/>
+      <c r="BO265" t="inlineStr"/>
+      <c r="BP265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>bFbpC2ej</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>45499.85416666666</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flores g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trinity health stadium
+  east hartford  ct </t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="K266" t="n">
+        <v>44</v>
+      </c>
+      <c r="L266" t="n">
+        <v>56</v>
+      </c>
+      <c r="M266" t="n">
+        <v>10</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>2</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>11</v>
+      </c>
+      <c r="R266" t="n">
+        <v>9</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="U266" t="n">
+        <v>167</v>
+      </c>
+      <c r="V266" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W266" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA266" t="inlineStr"/>
+      <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="inlineStr"/>
+      <c r="AD266" t="inlineStr"/>
+      <c r="AE266" t="inlineStr"/>
+      <c r="AF266" t="inlineStr"/>
+      <c r="AG266" t="inlineStr"/>
+      <c r="AH266" t="inlineStr"/>
+      <c r="AI266" t="inlineStr"/>
+      <c r="AJ266" t="inlineStr"/>
+      <c r="AK266" t="inlineStr"/>
+      <c r="AL266" t="inlineStr"/>
+      <c r="AM266" t="inlineStr"/>
+      <c r="AN266" t="inlineStr"/>
+      <c r="AO266" t="inlineStr"/>
+      <c r="AP266" t="inlineStr"/>
+      <c r="AQ266" t="inlineStr"/>
+      <c r="AR266" t="inlineStr"/>
+      <c r="AS266" t="inlineStr"/>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AU266" t="inlineStr"/>
+      <c r="AV266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr"/>
+      <c r="AX266" t="inlineStr"/>
+      <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr"/>
+      <c r="BA266" t="inlineStr"/>
+      <c r="BB266" t="inlineStr"/>
+      <c r="BC266" t="inlineStr"/>
+      <c r="BD266" t="inlineStr"/>
+      <c r="BE266" t="inlineStr"/>
+      <c r="BF266" t="inlineStr"/>
+      <c r="BG266" t="inlineStr"/>
+      <c r="BH266" t="inlineStr"/>
+      <c r="BI266" t="inlineStr"/>
+      <c r="BJ266" t="inlineStr"/>
+      <c r="BK266" t="inlineStr"/>
+      <c r="BL266" t="inlineStr"/>
+      <c r="BM266" t="inlineStr"/>
+      <c r="BN266" t="inlineStr"/>
+      <c r="BO266" t="inlineStr"/>
+      <c r="BP266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>nHKFVjdB</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>45497.5</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kilpatrick a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">segra field
+  leesburg  va </t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F267" t="n">
+        <v>2512</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>2</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="K267" t="n">
+        <v>50</v>
+      </c>
+      <c r="L267" t="n">
+        <v>50</v>
+      </c>
+      <c r="M267" t="n">
+        <v>12</v>
+      </c>
+      <c r="N267" t="n">
+        <v>10</v>
+      </c>
+      <c r="O267" t="n">
+        <v>6</v>
+      </c>
+      <c r="P267" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>15</v>
+      </c>
+      <c r="R267" t="n">
+        <v>14</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="U267" t="n">
+        <v>167</v>
+      </c>
+      <c r="V267" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W267" t="n">
+        <v>0</v>
+      </c>
+      <c r="X267" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA267" t="inlineStr"/>
+      <c r="AB267" t="inlineStr"/>
+      <c r="AC267" t="inlineStr"/>
+      <c r="AD267" t="inlineStr"/>
+      <c r="AE267" t="inlineStr"/>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="inlineStr"/>
+      <c r="AH267" t="inlineStr"/>
+      <c r="AI267" t="inlineStr"/>
+      <c r="AJ267" t="inlineStr"/>
+      <c r="AK267" t="inlineStr"/>
+      <c r="AL267" t="inlineStr"/>
+      <c r="AM267" t="inlineStr"/>
+      <c r="AN267" t="inlineStr"/>
+      <c r="AO267" t="inlineStr"/>
+      <c r="AP267" t="inlineStr"/>
+      <c r="AQ267" t="inlineStr"/>
+      <c r="AR267" t="inlineStr"/>
+      <c r="AS267" t="inlineStr"/>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AU267" t="inlineStr"/>
+      <c r="AV267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr"/>
+      <c r="AX267" t="inlineStr"/>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr"/>
+      <c r="BA267" t="inlineStr"/>
+      <c r="BB267" t="inlineStr"/>
+      <c r="BC267" t="inlineStr"/>
+      <c r="BD267" t="inlineStr"/>
+      <c r="BE267" t="inlineStr"/>
+      <c r="BF267" t="inlineStr"/>
+      <c r="BG267" t="inlineStr"/>
+      <c r="BH267" t="inlineStr"/>
+      <c r="BI267" t="inlineStr"/>
+      <c r="BJ267" t="inlineStr"/>
+      <c r="BK267" t="inlineStr"/>
+      <c r="BL267" t="inlineStr"/>
+      <c r="BM267" t="inlineStr"/>
+      <c r="BN267" t="inlineStr"/>
+      <c r="BO267" t="inlineStr"/>
+      <c r="BP267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>00I3YhCh</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>45494.70833333334</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pioneer stadium
+  hayward  ca </t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F268" t="n">
+        <v>5446</v>
+      </c>
+      <c r="G268" t="n">
+        <v>2</v>
+      </c>
+      <c r="H268" t="n">
+        <v>5</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="K268" t="n">
+        <v>49</v>
+      </c>
+      <c r="L268" t="n">
+        <v>51</v>
+      </c>
+      <c r="M268" t="n">
+        <v>6</v>
+      </c>
+      <c r="N268" t="n">
+        <v>13</v>
+      </c>
+      <c r="O268" t="n">
+        <v>4</v>
+      </c>
+      <c r="P268" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>20</v>
+      </c>
+      <c r="R268" t="n">
+        <v>27</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="U268" t="n">
+        <v>167</v>
+      </c>
+      <c r="V268" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W268" t="n">
+        <v>0</v>
+      </c>
+      <c r="X268" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA268" t="inlineStr"/>
+      <c r="AB268" t="inlineStr"/>
+      <c r="AC268" t="inlineStr"/>
+      <c r="AD268" t="inlineStr"/>
+      <c r="AE268" t="inlineStr"/>
+      <c r="AF268" t="inlineStr"/>
+      <c r="AG268" t="inlineStr"/>
+      <c r="AH268" t="inlineStr"/>
+      <c r="AI268" t="inlineStr"/>
+      <c r="AJ268" t="inlineStr"/>
+      <c r="AK268" t="inlineStr"/>
+      <c r="AL268" t="inlineStr"/>
+      <c r="AM268" t="inlineStr"/>
+      <c r="AN268" t="inlineStr"/>
+      <c r="AO268" t="inlineStr"/>
+      <c r="AP268" t="inlineStr"/>
+      <c r="AQ268" t="inlineStr"/>
+      <c r="AR268" t="inlineStr"/>
+      <c r="AS268" t="inlineStr"/>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AU268" t="inlineStr"/>
+      <c r="AV268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr"/>
+      <c r="AX268" t="inlineStr"/>
+      <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr"/>
+      <c r="BA268" t="inlineStr"/>
+      <c r="BB268" t="inlineStr"/>
+      <c r="BC268" t="inlineStr"/>
+      <c r="BD268" t="inlineStr"/>
+      <c r="BE268" t="inlineStr"/>
+      <c r="BF268" t="inlineStr"/>
+      <c r="BG268" t="inlineStr"/>
+      <c r="BH268" t="inlineStr"/>
+      <c r="BI268" t="inlineStr"/>
+      <c r="BJ268" t="inlineStr"/>
+      <c r="BK268" t="inlineStr"/>
+      <c r="BL268" t="inlineStr"/>
+      <c r="BM268" t="inlineStr"/>
+      <c r="BN268" t="inlineStr"/>
+      <c r="BO268" t="inlineStr"/>
+      <c r="BP268" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP346"/>
+  <dimension ref="A1:BP362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61295,6 +61295,2670 @@
       <c r="BO346" t="inlineStr"/>
       <c r="BP346" t="inlineStr"/>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>trWntSE7</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="n">
+        <v>45542.97916666666</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F347" t="n">
+        <v>23188</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="n">
+        <v>0</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="K347" t="n">
+        <v>50</v>
+      </c>
+      <c r="L347" t="n">
+        <v>50</v>
+      </c>
+      <c r="M347" t="n">
+        <v>15</v>
+      </c>
+      <c r="N347" t="n">
+        <v>5</v>
+      </c>
+      <c r="O347" t="n">
+        <v>5</v>
+      </c>
+      <c r="P347" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>11</v>
+      </c>
+      <c r="R347" t="n">
+        <v>7</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="U347" t="n">
+        <v>167</v>
+      </c>
+      <c r="V347" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W347" t="n">
+        <v>0</v>
+      </c>
+      <c r="X347" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y347" t="inlineStr"/>
+      <c r="Z347" t="inlineStr"/>
+      <c r="AA347" t="inlineStr"/>
+      <c r="AB347" t="inlineStr"/>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE347" t="n">
+        <v>25.09090909090909</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>180.7272727272727</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH347" t="n">
+        <v>66.45454545454545</v>
+      </c>
+      <c r="AI347" t="n">
+        <v>1231818.181818182</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>69.90909090909091</v>
+      </c>
+      <c r="AK347" t="n">
+        <v>27.63636363636364</v>
+      </c>
+      <c r="AL347" t="n">
+        <v>181.1818181818182</v>
+      </c>
+      <c r="AM347" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN347" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="AO347" t="n">
+        <v>2845454.545454545</v>
+      </c>
+      <c r="AP347" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="AQ347" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AR347" t="n">
+        <v>180.9285714285714</v>
+      </c>
+      <c r="AS347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT347" t="n">
+        <v>66.28571428571429</v>
+      </c>
+      <c r="AU347" t="n">
+        <v>1203571.428571429</v>
+      </c>
+      <c r="AV347" t="n">
+        <v>69.71428571428571</v>
+      </c>
+      <c r="AW347" t="n">
+        <v>22.17647058823529</v>
+      </c>
+      <c r="AX347" t="n">
+        <v>179.1764705882353</v>
+      </c>
+      <c r="AY347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ347" t="n">
+        <v>63.94117647058823</v>
+      </c>
+      <c r="BA347" t="n">
+        <v>3711764.705882353</v>
+      </c>
+      <c r="BB347" t="n">
+        <v>72.47058823529412</v>
+      </c>
+      <c r="BC347" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD347" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BE347" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF347" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG347" t="n">
+        <v>181</v>
+      </c>
+      <c r="BH347" t="n">
+        <v>2110000</v>
+      </c>
+      <c r="BI347" t="n">
+        <v>210</v>
+      </c>
+      <c r="BJ347" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK347" t="n">
+        <v>180</v>
+      </c>
+      <c r="BL347" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM347" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN347" t="n">
+        <v>195</v>
+      </c>
+      <c r="BO347" t="n">
+        <v>3650000</v>
+      </c>
+      <c r="BP347" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>SvbdWyTh</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="n">
+        <v>45542.89583333334</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F348" t="n">
+        <v>16426</v>
+      </c>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="n">
+        <v>2</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="K348" t="n">
+        <v>65</v>
+      </c>
+      <c r="L348" t="n">
+        <v>35</v>
+      </c>
+      <c r="M348" t="n">
+        <v>5</v>
+      </c>
+      <c r="N348" t="n">
+        <v>9</v>
+      </c>
+      <c r="O348" t="n">
+        <v>2</v>
+      </c>
+      <c r="P348" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>10</v>
+      </c>
+      <c r="R348" t="n">
+        <v>12</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="U348" t="n">
+        <v>167</v>
+      </c>
+      <c r="V348" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W348" t="n">
+        <v>0</v>
+      </c>
+      <c r="X348" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y348" t="inlineStr"/>
+      <c r="Z348" t="inlineStr"/>
+      <c r="AA348" t="inlineStr"/>
+      <c r="AB348" t="inlineStr"/>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr"/>
+      <c r="AE348" t="n">
+        <v>25.18181818181818</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AH348" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AI348" t="n">
+        <v>2372727.272727273</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AK348" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AL348" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AM348" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN348" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AO348" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="AP348" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="AQ348" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AR348" t="n">
+        <v>179.4285714285714</v>
+      </c>
+      <c r="AS348" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AT348" t="n">
+        <v>62.09523809523809</v>
+      </c>
+      <c r="AU348" t="n">
+        <v>745714.2857142857</v>
+      </c>
+      <c r="AV348" t="n">
+        <v>65.85714285714286</v>
+      </c>
+      <c r="AW348" t="n">
+        <v>24.44444444444444</v>
+      </c>
+      <c r="AX348" t="n">
+        <v>181.9444444444445</v>
+      </c>
+      <c r="AY348" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AZ348" t="n">
+        <v>62.22222222222222</v>
+      </c>
+      <c r="BA348" t="n">
+        <v>992777.7777777778</v>
+      </c>
+      <c r="BB348" t="n">
+        <v>68.61111111111111</v>
+      </c>
+      <c r="BC348" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="BD348" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE348" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF348" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG348" t="n">
+        <v>258</v>
+      </c>
+      <c r="BH348" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BI348" t="n">
+        <v>276</v>
+      </c>
+      <c r="BJ348" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="BK348" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL348" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM348" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN348" t="n">
+        <v>177</v>
+      </c>
+      <c r="BO348" t="n">
+        <v>2050000</v>
+      </c>
+      <c r="BP348" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="n">
+        <v>45542.89583333334</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="K349" t="n">
+        <v>63</v>
+      </c>
+      <c r="L349" t="n">
+        <v>37</v>
+      </c>
+      <c r="M349" t="n">
+        <v>11</v>
+      </c>
+      <c r="N349" t="n">
+        <v>8</v>
+      </c>
+      <c r="O349" t="n">
+        <v>4</v>
+      </c>
+      <c r="P349" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>13</v>
+      </c>
+      <c r="R349" t="n">
+        <v>14</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="U349" t="n">
+        <v>167</v>
+      </c>
+      <c r="V349" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W349" t="n">
+        <v>0</v>
+      </c>
+      <c r="X349" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y349" t="inlineStr"/>
+      <c r="Z349" t="inlineStr"/>
+      <c r="AA349" t="inlineStr"/>
+      <c r="AB349" t="inlineStr"/>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr"/>
+      <c r="AE349" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH349" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="AI349" t="n">
+        <v>1975500</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="AK349" t="n">
+        <v>30.09090909090909</v>
+      </c>
+      <c r="AL349" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="AM349" t="n">
+        <v>1.454545454545455</v>
+      </c>
+      <c r="AN349" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AO349" t="n">
+        <v>3352272.727272727</v>
+      </c>
+      <c r="AP349" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="AQ349" t="n">
+        <v>24.58333333333333</v>
+      </c>
+      <c r="AR349" t="n">
+        <v>177</v>
+      </c>
+      <c r="AS349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT349" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AU349" t="n">
+        <v>1354166.666666667</v>
+      </c>
+      <c r="AV349" t="n">
+        <v>70.16666666666667</v>
+      </c>
+      <c r="AW349" t="n">
+        <v>21.27272727272727</v>
+      </c>
+      <c r="AX349" t="n">
+        <v>176.6363636363636</v>
+      </c>
+      <c r="AY349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ349" t="n">
+        <v>61.27272727272727</v>
+      </c>
+      <c r="BA349" t="n">
+        <v>1022727.272727273</v>
+      </c>
+      <c r="BB349" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="BC349" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD349" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BE349" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF349" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG349" t="n">
+        <v>114</v>
+      </c>
+      <c r="BH349" t="n">
+        <v>1055000</v>
+      </c>
+      <c r="BI349" t="n">
+        <v>135</v>
+      </c>
+      <c r="BJ349" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="BK349" t="n">
+        <v>181.2857142857143</v>
+      </c>
+      <c r="BL349" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="BM349" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN349" t="n">
+        <v>484</v>
+      </c>
+      <c r="BO349" t="n">
+        <v>30600000</v>
+      </c>
+      <c r="BP349" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>hIoLKAg0</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F350" t="n">
+        <v>20523</v>
+      </c>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+      <c r="H350" t="n">
+        <v>4</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="K350" t="n">
+        <v>55</v>
+      </c>
+      <c r="L350" t="n">
+        <v>45</v>
+      </c>
+      <c r="M350" t="n">
+        <v>10</v>
+      </c>
+      <c r="N350" t="n">
+        <v>15</v>
+      </c>
+      <c r="O350" t="n">
+        <v>1</v>
+      </c>
+      <c r="P350" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>8</v>
+      </c>
+      <c r="R350" t="n">
+        <v>7</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="U350" t="n">
+        <v>167</v>
+      </c>
+      <c r="V350" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W350" t="n">
+        <v>0</v>
+      </c>
+      <c r="X350" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y350" t="inlineStr"/>
+      <c r="Z350" t="inlineStr"/>
+      <c r="AA350" t="inlineStr"/>
+      <c r="AB350" t="inlineStr"/>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="AE350" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH350" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="AI350" t="n">
+        <v>1977777.777777778</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>71.22222222222223</v>
+      </c>
+      <c r="AK350" t="n">
+        <v>24.88888888888889</v>
+      </c>
+      <c r="AL350" t="n">
+        <v>180.8888888888889</v>
+      </c>
+      <c r="AM350" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AN350" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="AO350" t="n">
+        <v>2863333.333333333</v>
+      </c>
+      <c r="AP350" t="n">
+        <v>72.44444444444444</v>
+      </c>
+      <c r="AQ350" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AR350" t="n">
+        <v>181.8125</v>
+      </c>
+      <c r="AS350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT350" t="n">
+        <v>66.375</v>
+      </c>
+      <c r="AU350" t="n">
+        <v>1317187.5</v>
+      </c>
+      <c r="AV350" t="n">
+        <v>69.9375</v>
+      </c>
+      <c r="AW350" t="n">
+        <v>22.44444444444444</v>
+      </c>
+      <c r="AX350" t="n">
+        <v>179.7777777777778</v>
+      </c>
+      <c r="AY350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ350" t="n">
+        <v>63.83333333333334</v>
+      </c>
+      <c r="BA350" t="n">
+        <v>1869722.222222222</v>
+      </c>
+      <c r="BB350" t="n">
+        <v>71.61111111111111</v>
+      </c>
+      <c r="BC350" t="n">
+        <v>27.16666666666667</v>
+      </c>
+      <c r="BD350" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="BE350" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF350" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG350" t="n">
+        <v>408</v>
+      </c>
+      <c r="BH350" t="n">
+        <v>26050000</v>
+      </c>
+      <c r="BI350" t="n">
+        <v>424</v>
+      </c>
+      <c r="BJ350" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BK350" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="BL350" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM350" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN350" t="n">
+        <v>286</v>
+      </c>
+      <c r="BO350" t="n">
+        <v>10150000</v>
+      </c>
+      <c r="BP350" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>KEflYcbt</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F351" t="n">
+        <v>30512</v>
+      </c>
+      <c r="G351" t="n">
+        <v>2</v>
+      </c>
+      <c r="H351" t="n">
+        <v>2</v>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="K351" t="n">
+        <v>55</v>
+      </c>
+      <c r="L351" t="n">
+        <v>45</v>
+      </c>
+      <c r="M351" t="n">
+        <v>10</v>
+      </c>
+      <c r="N351" t="n">
+        <v>24</v>
+      </c>
+      <c r="O351" t="n">
+        <v>4</v>
+      </c>
+      <c r="P351" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>9</v>
+      </c>
+      <c r="R351" t="n">
+        <v>15</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="U351" t="n">
+        <v>167</v>
+      </c>
+      <c r="V351" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W351" t="n">
+        <v>0</v>
+      </c>
+      <c r="X351" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y351" t="inlineStr"/>
+      <c r="Z351" t="inlineStr"/>
+      <c r="AA351" t="inlineStr"/>
+      <c r="AB351" t="inlineStr"/>
+      <c r="AC351" t="inlineStr"/>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="AE351" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>180.7777777777778</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AH351" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AI351" t="n">
+        <v>3436111.111111111</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>72.44444444444444</v>
+      </c>
+      <c r="AK351" t="n">
+        <v>25.72727272727273</v>
+      </c>
+      <c r="AL351" t="n">
+        <v>184</v>
+      </c>
+      <c r="AM351" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AN351" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="AO351" t="n">
+        <v>2588636.363636364</v>
+      </c>
+      <c r="AP351" t="n">
+        <v>72.09090909090909</v>
+      </c>
+      <c r="AQ351" t="n">
+        <v>27.64285714285714</v>
+      </c>
+      <c r="AR351" t="n">
+        <v>179.2142857142857</v>
+      </c>
+      <c r="AS351" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="AT351" t="n">
+        <v>67.28571428571429</v>
+      </c>
+      <c r="AU351" t="n">
+        <v>1401785.714285714</v>
+      </c>
+      <c r="AV351" t="n">
+        <v>69.07142857142857</v>
+      </c>
+      <c r="AW351" t="n">
+        <v>24.42105263157895</v>
+      </c>
+      <c r="AX351" t="n">
+        <v>182.421052631579</v>
+      </c>
+      <c r="AY351" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ351" t="n">
+        <v>65.42105263157895</v>
+      </c>
+      <c r="BA351" t="n">
+        <v>1622368.421052632</v>
+      </c>
+      <c r="BB351" t="n">
+        <v>69.57894736842105</v>
+      </c>
+      <c r="BC351" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BD351" t="n">
+        <v>182</v>
+      </c>
+      <c r="BE351" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF351" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG351" t="n">
+        <v>212</v>
+      </c>
+      <c r="BH351" t="n">
+        <v>10025000</v>
+      </c>
+      <c r="BI351" t="n">
+        <v>215</v>
+      </c>
+      <c r="BJ351" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK351" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="BL351" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM351" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN351" t="n">
+        <v>201</v>
+      </c>
+      <c r="BO351" t="n">
+        <v>3975000</v>
+      </c>
+      <c r="BP351" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>EyfhXHDn</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F352" t="n">
+        <v>17708</v>
+      </c>
+      <c r="G352" t="n">
+        <v>1</v>
+      </c>
+      <c r="H352" t="n">
+        <v>1</v>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="K352" t="n">
+        <v>58</v>
+      </c>
+      <c r="L352" t="n">
+        <v>42</v>
+      </c>
+      <c r="M352" t="n">
+        <v>10</v>
+      </c>
+      <c r="N352" t="n">
+        <v>4</v>
+      </c>
+      <c r="O352" t="n">
+        <v>3</v>
+      </c>
+      <c r="P352" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>12</v>
+      </c>
+      <c r="R352" t="n">
+        <v>20</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>KIxd2dNg</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="U352" t="n">
+        <v>167</v>
+      </c>
+      <c r="V352" t="n">
+        <v>1671</v>
+      </c>
+      <c r="W352" t="n">
+        <v>0</v>
+      </c>
+      <c r="X352" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y352" t="inlineStr"/>
+      <c r="Z352" t="inlineStr"/>
+      <c r="AA352" t="inlineStr"/>
+      <c r="AB352" t="inlineStr"/>
+      <c r="AC352" t="inlineStr"/>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="AE352" t="n">
+        <v>23.36363636363636</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>181.8181818181818</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH352" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="AI352" t="n">
+        <v>1363181.818181818</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AK352" t="n">
+        <v>28.27272727272727</v>
+      </c>
+      <c r="AL352" t="n">
+        <v>180.6363636363636</v>
+      </c>
+      <c r="AM352" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AN352" t="n">
+        <v>67.54545454545455</v>
+      </c>
+      <c r="AO352" t="n">
+        <v>1335454.545454545</v>
+      </c>
+      <c r="AP352" t="n">
+        <v>69.36363636363636</v>
+      </c>
+      <c r="AQ352" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR352" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AS352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT352" t="n">
+        <v>62.13333333333333</v>
+      </c>
+      <c r="AU352" t="n">
+        <v>1407666.666666667</v>
+      </c>
+      <c r="AV352" t="n">
+        <v>73.86666666666666</v>
+      </c>
+      <c r="AW352" t="n">
+        <v>26.93333333333333</v>
+      </c>
+      <c r="AX352" t="n">
+        <v>179.7333333333333</v>
+      </c>
+      <c r="AY352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ352" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="BA352" t="n">
+        <v>955000</v>
+      </c>
+      <c r="BB352" t="n">
+        <v>67.26666666666667</v>
+      </c>
+      <c r="BC352" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="BD352" t="n">
+        <v>182</v>
+      </c>
+      <c r="BE352" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BF352" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG352" t="n">
+        <v>400</v>
+      </c>
+      <c r="BH352" t="n">
+        <v>27400000</v>
+      </c>
+      <c r="BI352" t="n">
+        <v>436</v>
+      </c>
+      <c r="BJ352" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BK352" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="BL352" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM352" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN352" t="n">
+        <v>327</v>
+      </c>
+      <c r="BO352" t="n">
+        <v>5850000</v>
+      </c>
+      <c r="BP352" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>ryEQJ8Fk</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="n">
+        <v>45542.95833333334</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardinale stadium
+  seaside  ca </t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F353" t="n">
+        <v>3827</v>
+      </c>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+      <c r="H353" t="n">
+        <v>1</v>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>8njPmvTl</t>
+        </is>
+      </c>
+      <c r="K353" t="n">
+        <v>66</v>
+      </c>
+      <c r="L353" t="n">
+        <v>34</v>
+      </c>
+      <c r="M353" t="n">
+        <v>14</v>
+      </c>
+      <c r="N353" t="n">
+        <v>4</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+      <c r="P353" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>16</v>
+      </c>
+      <c r="R353" t="n">
+        <v>11</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>4jMOGgL1</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>6X9nrWKc</t>
+        </is>
+      </c>
+      <c r="U353" t="n">
+        <v>167</v>
+      </c>
+      <c r="V353" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W353" t="n">
+        <v>0</v>
+      </c>
+      <c r="X353" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA353" t="inlineStr"/>
+      <c r="AB353" t="inlineStr"/>
+      <c r="AC353" t="inlineStr"/>
+      <c r="AD353" t="inlineStr"/>
+      <c r="AE353" t="inlineStr"/>
+      <c r="AF353" t="inlineStr"/>
+      <c r="AG353" t="inlineStr"/>
+      <c r="AH353" t="inlineStr"/>
+      <c r="AI353" t="inlineStr"/>
+      <c r="AJ353" t="inlineStr"/>
+      <c r="AK353" t="inlineStr"/>
+      <c r="AL353" t="inlineStr"/>
+      <c r="AM353" t="inlineStr"/>
+      <c r="AN353" t="inlineStr"/>
+      <c r="AO353" t="inlineStr"/>
+      <c r="AP353" t="inlineStr"/>
+      <c r="AQ353" t="inlineStr"/>
+      <c r="AR353" t="inlineStr"/>
+      <c r="AS353" t="inlineStr"/>
+      <c r="AT353" t="inlineStr"/>
+      <c r="AU353" t="inlineStr"/>
+      <c r="AV353" t="inlineStr"/>
+      <c r="AW353" t="inlineStr"/>
+      <c r="AX353" t="inlineStr"/>
+      <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr"/>
+      <c r="BA353" t="inlineStr"/>
+      <c r="BB353" t="inlineStr"/>
+      <c r="BC353" t="inlineStr"/>
+      <c r="BD353" t="inlineStr"/>
+      <c r="BE353" t="inlineStr"/>
+      <c r="BF353" t="inlineStr"/>
+      <c r="BG353" t="inlineStr"/>
+      <c r="BH353" t="inlineStr"/>
+      <c r="BI353" t="inlineStr"/>
+      <c r="BJ353" t="inlineStr"/>
+      <c r="BK353" t="inlineStr"/>
+      <c r="BL353" t="inlineStr"/>
+      <c r="BM353" t="inlineStr"/>
+      <c r="BN353" t="inlineStr"/>
+      <c r="BO353" t="inlineStr"/>
+      <c r="BP353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>nTYkQAxM</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="n">
+        <v>45542.91666666666</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scheer j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weidner field
+  colorado springs  co </t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F354" t="n">
+        <v>7362</v>
+      </c>
+      <c r="G354" t="n">
+        <v>4</v>
+      </c>
+      <c r="H354" t="n">
+        <v>2</v>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K354" t="n">
+        <v>50</v>
+      </c>
+      <c r="L354" t="n">
+        <v>50</v>
+      </c>
+      <c r="M354" t="n">
+        <v>20</v>
+      </c>
+      <c r="N354" t="n">
+        <v>19</v>
+      </c>
+      <c r="O354" t="n">
+        <v>10</v>
+      </c>
+      <c r="P354" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>8</v>
+      </c>
+      <c r="R354" t="n">
+        <v>8</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>SUJLjQfn</t>
+        </is>
+      </c>
+      <c r="U354" t="n">
+        <v>167</v>
+      </c>
+      <c r="V354" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W354" t="n">
+        <v>0</v>
+      </c>
+      <c r="X354" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA354" t="inlineStr"/>
+      <c r="AB354" t="inlineStr"/>
+      <c r="AC354" t="inlineStr"/>
+      <c r="AD354" t="inlineStr"/>
+      <c r="AE354" t="inlineStr"/>
+      <c r="AF354" t="inlineStr"/>
+      <c r="AG354" t="inlineStr"/>
+      <c r="AH354" t="inlineStr"/>
+      <c r="AI354" t="inlineStr"/>
+      <c r="AJ354" t="inlineStr"/>
+      <c r="AK354" t="inlineStr"/>
+      <c r="AL354" t="inlineStr"/>
+      <c r="AM354" t="inlineStr"/>
+      <c r="AN354" t="inlineStr"/>
+      <c r="AO354" t="inlineStr"/>
+      <c r="AP354" t="inlineStr"/>
+      <c r="AQ354" t="inlineStr"/>
+      <c r="AR354" t="inlineStr"/>
+      <c r="AS354" t="inlineStr"/>
+      <c r="AT354" t="inlineStr"/>
+      <c r="AU354" t="inlineStr"/>
+      <c r="AV354" t="inlineStr"/>
+      <c r="AW354" t="inlineStr"/>
+      <c r="AX354" t="inlineStr"/>
+      <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr"/>
+      <c r="BA354" t="inlineStr"/>
+      <c r="BB354" t="inlineStr"/>
+      <c r="BC354" t="inlineStr"/>
+      <c r="BD354" t="inlineStr"/>
+      <c r="BE354" t="inlineStr"/>
+      <c r="BF354" t="inlineStr"/>
+      <c r="BG354" t="inlineStr"/>
+      <c r="BH354" t="inlineStr"/>
+      <c r="BI354" t="inlineStr"/>
+      <c r="BJ354" t="inlineStr"/>
+      <c r="BK354" t="inlineStr"/>
+      <c r="BL354" t="inlineStr"/>
+      <c r="BM354" t="inlineStr"/>
+      <c r="BN354" t="inlineStr"/>
+      <c r="BO354" t="inlineStr"/>
+      <c r="BP354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>QJXgPUiS</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="n">
+        <v>45542.91666666666</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arroyo l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">southwest university park
+  el paso  tx </t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F355" t="n">
+        <v>5764</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="K355" t="n">
+        <v>60</v>
+      </c>
+      <c r="L355" t="n">
+        <v>40</v>
+      </c>
+      <c r="M355" t="n">
+        <v>5</v>
+      </c>
+      <c r="N355" t="n">
+        <v>9</v>
+      </c>
+      <c r="O355" t="n">
+        <v>2</v>
+      </c>
+      <c r="P355" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>5</v>
+      </c>
+      <c r="R355" t="n">
+        <v>19</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="U355" t="n">
+        <v>167</v>
+      </c>
+      <c r="V355" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W355" t="n">
+        <v>0</v>
+      </c>
+      <c r="X355" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA355" t="inlineStr"/>
+      <c r="AB355" t="inlineStr"/>
+      <c r="AC355" t="inlineStr"/>
+      <c r="AD355" t="inlineStr"/>
+      <c r="AE355" t="inlineStr"/>
+      <c r="AF355" t="inlineStr"/>
+      <c r="AG355" t="inlineStr"/>
+      <c r="AH355" t="inlineStr"/>
+      <c r="AI355" t="inlineStr"/>
+      <c r="AJ355" t="inlineStr"/>
+      <c r="AK355" t="inlineStr"/>
+      <c r="AL355" t="inlineStr"/>
+      <c r="AM355" t="inlineStr"/>
+      <c r="AN355" t="inlineStr"/>
+      <c r="AO355" t="inlineStr"/>
+      <c r="AP355" t="inlineStr"/>
+      <c r="AQ355" t="inlineStr"/>
+      <c r="AR355" t="inlineStr"/>
+      <c r="AS355" t="inlineStr"/>
+      <c r="AT355" t="inlineStr"/>
+      <c r="AU355" t="inlineStr"/>
+      <c r="AV355" t="inlineStr"/>
+      <c r="AW355" t="inlineStr"/>
+      <c r="AX355" t="inlineStr"/>
+      <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr"/>
+      <c r="BA355" t="inlineStr"/>
+      <c r="BB355" t="inlineStr"/>
+      <c r="BC355" t="inlineStr"/>
+      <c r="BD355" t="inlineStr"/>
+      <c r="BE355" t="inlineStr"/>
+      <c r="BF355" t="inlineStr"/>
+      <c r="BG355" t="inlineStr"/>
+      <c r="BH355" t="inlineStr"/>
+      <c r="BI355" t="inlineStr"/>
+      <c r="BJ355" t="inlineStr"/>
+      <c r="BK355" t="inlineStr"/>
+      <c r="BL355" t="inlineStr"/>
+      <c r="BM355" t="inlineStr"/>
+      <c r="BN355" t="inlineStr"/>
+      <c r="BO355" t="inlineStr"/>
+      <c r="BP355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>IgUoRjNF</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nichols a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriots point soccer complex
+  mount pleasant  sc </t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F356" t="n">
+        <v>3525</v>
+      </c>
+      <c r="G356" t="n">
+        <v>2</v>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="K356" t="n">
+        <v>60</v>
+      </c>
+      <c r="L356" t="n">
+        <v>40</v>
+      </c>
+      <c r="M356" t="n">
+        <v>14</v>
+      </c>
+      <c r="N356" t="n">
+        <v>11</v>
+      </c>
+      <c r="O356" t="n">
+        <v>5</v>
+      </c>
+      <c r="P356" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>13</v>
+      </c>
+      <c r="R356" t="n">
+        <v>12</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="U356" t="n">
+        <v>167</v>
+      </c>
+      <c r="V356" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W356" t="n">
+        <v>0</v>
+      </c>
+      <c r="X356" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA356" t="inlineStr"/>
+      <c r="AB356" t="inlineStr"/>
+      <c r="AC356" t="inlineStr"/>
+      <c r="AD356" t="inlineStr"/>
+      <c r="AE356" t="inlineStr"/>
+      <c r="AF356" t="inlineStr"/>
+      <c r="AG356" t="inlineStr"/>
+      <c r="AH356" t="inlineStr"/>
+      <c r="AI356" t="inlineStr"/>
+      <c r="AJ356" t="inlineStr"/>
+      <c r="AK356" t="inlineStr"/>
+      <c r="AL356" t="inlineStr"/>
+      <c r="AM356" t="inlineStr"/>
+      <c r="AN356" t="inlineStr"/>
+      <c r="AO356" t="inlineStr"/>
+      <c r="AP356" t="inlineStr"/>
+      <c r="AQ356" t="inlineStr"/>
+      <c r="AR356" t="inlineStr"/>
+      <c r="AS356" t="inlineStr"/>
+      <c r="AT356" t="inlineStr"/>
+      <c r="AU356" t="inlineStr"/>
+      <c r="AV356" t="inlineStr"/>
+      <c r="AW356" t="inlineStr"/>
+      <c r="AX356" t="inlineStr"/>
+      <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr"/>
+      <c r="BA356" t="inlineStr"/>
+      <c r="BB356" t="inlineStr"/>
+      <c r="BC356" t="inlineStr"/>
+      <c r="BD356" t="inlineStr"/>
+      <c r="BE356" t="inlineStr"/>
+      <c r="BF356" t="inlineStr"/>
+      <c r="BG356" t="inlineStr"/>
+      <c r="BH356" t="inlineStr"/>
+      <c r="BI356" t="inlineStr"/>
+      <c r="BJ356" t="inlineStr"/>
+      <c r="BK356" t="inlineStr"/>
+      <c r="BL356" t="inlineStr"/>
+      <c r="BM356" t="inlineStr"/>
+      <c r="BN356" t="inlineStr"/>
+      <c r="BO356" t="inlineStr"/>
+      <c r="BP356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>xbDUISUe</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="n">
+        <v>45542.85416666666</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmanovic e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wakemed soccer park
+  cary  nc </t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="n">
+        <v>5</v>
+      </c>
+      <c r="H357" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="K357" t="n">
+        <v>44</v>
+      </c>
+      <c r="L357" t="n">
+        <v>56</v>
+      </c>
+      <c r="M357" t="n">
+        <v>23</v>
+      </c>
+      <c r="N357" t="n">
+        <v>9</v>
+      </c>
+      <c r="O357" t="n">
+        <v>9</v>
+      </c>
+      <c r="P357" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>18</v>
+      </c>
+      <c r="R357" t="n">
+        <v>9</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="U357" t="n">
+        <v>167</v>
+      </c>
+      <c r="V357" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W357" t="n">
+        <v>0</v>
+      </c>
+      <c r="X357" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA357" t="inlineStr"/>
+      <c r="AB357" t="inlineStr"/>
+      <c r="AC357" t="inlineStr"/>
+      <c r="AD357" t="inlineStr"/>
+      <c r="AE357" t="inlineStr"/>
+      <c r="AF357" t="inlineStr"/>
+      <c r="AG357" t="inlineStr"/>
+      <c r="AH357" t="inlineStr"/>
+      <c r="AI357" t="inlineStr"/>
+      <c r="AJ357" t="inlineStr"/>
+      <c r="AK357" t="inlineStr"/>
+      <c r="AL357" t="inlineStr"/>
+      <c r="AM357" t="inlineStr"/>
+      <c r="AN357" t="inlineStr"/>
+      <c r="AO357" t="inlineStr"/>
+      <c r="AP357" t="inlineStr"/>
+      <c r="AQ357" t="inlineStr"/>
+      <c r="AR357" t="inlineStr"/>
+      <c r="AS357" t="inlineStr"/>
+      <c r="AT357" t="inlineStr"/>
+      <c r="AU357" t="inlineStr"/>
+      <c r="AV357" t="inlineStr"/>
+      <c r="AW357" t="inlineStr"/>
+      <c r="AX357" t="inlineStr"/>
+      <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr"/>
+      <c r="BA357" t="inlineStr"/>
+      <c r="BB357" t="inlineStr"/>
+      <c r="BC357" t="inlineStr"/>
+      <c r="BD357" t="inlineStr"/>
+      <c r="BE357" t="inlineStr"/>
+      <c r="BF357" t="inlineStr"/>
+      <c r="BG357" t="inlineStr"/>
+      <c r="BH357" t="inlineStr"/>
+      <c r="BI357" t="inlineStr"/>
+      <c r="BJ357" t="inlineStr"/>
+      <c r="BK357" t="inlineStr"/>
+      <c r="BL357" t="inlineStr"/>
+      <c r="BM357" t="inlineStr"/>
+      <c r="BN357" t="inlineStr"/>
+      <c r="BO357" t="inlineStr"/>
+      <c r="BP357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>W0AMKl0q</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="n">
+        <v>45542.83333333334</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snyder t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trinity health stadium
+  east hartford  ct </t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="K358" t="n">
+        <v>55</v>
+      </c>
+      <c r="L358" t="n">
+        <v>45</v>
+      </c>
+      <c r="M358" t="n">
+        <v>8</v>
+      </c>
+      <c r="N358" t="n">
+        <v>10</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0</v>
+      </c>
+      <c r="P358" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>7</v>
+      </c>
+      <c r="R358" t="n">
+        <v>10</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="U358" t="n">
+        <v>167</v>
+      </c>
+      <c r="V358" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W358" t="n">
+        <v>0</v>
+      </c>
+      <c r="X358" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA358" t="inlineStr"/>
+      <c r="AB358" t="inlineStr"/>
+      <c r="AC358" t="inlineStr"/>
+      <c r="AD358" t="inlineStr"/>
+      <c r="AE358" t="inlineStr"/>
+      <c r="AF358" t="inlineStr"/>
+      <c r="AG358" t="inlineStr"/>
+      <c r="AH358" t="inlineStr"/>
+      <c r="AI358" t="inlineStr"/>
+      <c r="AJ358" t="inlineStr"/>
+      <c r="AK358" t="inlineStr"/>
+      <c r="AL358" t="inlineStr"/>
+      <c r="AM358" t="inlineStr"/>
+      <c r="AN358" t="inlineStr"/>
+      <c r="AO358" t="inlineStr"/>
+      <c r="AP358" t="inlineStr"/>
+      <c r="AQ358" t="inlineStr"/>
+      <c r="AR358" t="inlineStr"/>
+      <c r="AS358" t="inlineStr"/>
+      <c r="AT358" t="inlineStr"/>
+      <c r="AU358" t="inlineStr"/>
+      <c r="AV358" t="inlineStr"/>
+      <c r="AW358" t="inlineStr"/>
+      <c r="AX358" t="inlineStr"/>
+      <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr"/>
+      <c r="BA358" t="inlineStr"/>
+      <c r="BB358" t="inlineStr"/>
+      <c r="BC358" t="inlineStr"/>
+      <c r="BD358" t="inlineStr"/>
+      <c r="BE358" t="inlineStr"/>
+      <c r="BF358" t="inlineStr"/>
+      <c r="BG358" t="inlineStr"/>
+      <c r="BH358" t="inlineStr"/>
+      <c r="BI358" t="inlineStr"/>
+      <c r="BJ358" t="inlineStr"/>
+      <c r="BK358" t="inlineStr"/>
+      <c r="BL358" t="inlineStr"/>
+      <c r="BM358" t="inlineStr"/>
+      <c r="BN358" t="inlineStr"/>
+      <c r="BO358" t="inlineStr"/>
+      <c r="BP358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>GlCYHnp2</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="n">
+        <v>45542.83333333334</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highmark stadium
+  pittsburgh  pa </t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F359" t="n">
+        <v>5619</v>
+      </c>
+      <c r="G359" t="n">
+        <v>2</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0</v>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="K359" t="n">
+        <v>38</v>
+      </c>
+      <c r="L359" t="n">
+        <v>62</v>
+      </c>
+      <c r="M359" t="n">
+        <v>6</v>
+      </c>
+      <c r="N359" t="n">
+        <v>2</v>
+      </c>
+      <c r="O359" t="n">
+        <v>3</v>
+      </c>
+      <c r="P359" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>15</v>
+      </c>
+      <c r="R359" t="n">
+        <v>13</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="U359" t="n">
+        <v>167</v>
+      </c>
+      <c r="V359" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W359" t="n">
+        <v>0</v>
+      </c>
+      <c r="X359" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA359" t="inlineStr"/>
+      <c r="AB359" t="inlineStr"/>
+      <c r="AC359" t="inlineStr"/>
+      <c r="AD359" t="inlineStr"/>
+      <c r="AE359" t="inlineStr"/>
+      <c r="AF359" t="inlineStr"/>
+      <c r="AG359" t="inlineStr"/>
+      <c r="AH359" t="inlineStr"/>
+      <c r="AI359" t="inlineStr"/>
+      <c r="AJ359" t="inlineStr"/>
+      <c r="AK359" t="inlineStr"/>
+      <c r="AL359" t="inlineStr"/>
+      <c r="AM359" t="inlineStr"/>
+      <c r="AN359" t="inlineStr"/>
+      <c r="AO359" t="inlineStr"/>
+      <c r="AP359" t="inlineStr"/>
+      <c r="AQ359" t="inlineStr"/>
+      <c r="AR359" t="inlineStr"/>
+      <c r="AS359" t="inlineStr"/>
+      <c r="AT359" t="inlineStr"/>
+      <c r="AU359" t="inlineStr"/>
+      <c r="AV359" t="inlineStr"/>
+      <c r="AW359" t="inlineStr"/>
+      <c r="AX359" t="inlineStr"/>
+      <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr"/>
+      <c r="BA359" t="inlineStr"/>
+      <c r="BB359" t="inlineStr"/>
+      <c r="BC359" t="inlineStr"/>
+      <c r="BD359" t="inlineStr"/>
+      <c r="BE359" t="inlineStr"/>
+      <c r="BF359" t="inlineStr"/>
+      <c r="BG359" t="inlineStr"/>
+      <c r="BH359" t="inlineStr"/>
+      <c r="BI359" t="inlineStr"/>
+      <c r="BJ359" t="inlineStr"/>
+      <c r="BK359" t="inlineStr"/>
+      <c r="BL359" t="inlineStr"/>
+      <c r="BM359" t="inlineStr"/>
+      <c r="BN359" t="inlineStr"/>
+      <c r="BO359" t="inlineStr"/>
+      <c r="BP359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>v3VsSW79</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="n">
+        <v>45542</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wild horse pass stadium
+  chandler  az </t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="K360" t="n">
+        <v>70</v>
+      </c>
+      <c r="L360" t="n">
+        <v>30</v>
+      </c>
+      <c r="M360" t="n">
+        <v>6</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" t="n">
+        <v>3</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>4</v>
+      </c>
+      <c r="R360" t="n">
+        <v>6</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>xYs9X2t2</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="U360" t="n">
+        <v>167</v>
+      </c>
+      <c r="V360" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W360" t="n">
+        <v>0</v>
+      </c>
+      <c r="X360" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA360" t="inlineStr"/>
+      <c r="AB360" t="inlineStr"/>
+      <c r="AC360" t="inlineStr"/>
+      <c r="AD360" t="inlineStr"/>
+      <c r="AE360" t="inlineStr"/>
+      <c r="AF360" t="inlineStr"/>
+      <c r="AG360" t="inlineStr"/>
+      <c r="AH360" t="inlineStr"/>
+      <c r="AI360" t="inlineStr"/>
+      <c r="AJ360" t="inlineStr"/>
+      <c r="AK360" t="inlineStr"/>
+      <c r="AL360" t="inlineStr"/>
+      <c r="AM360" t="inlineStr"/>
+      <c r="AN360" t="inlineStr"/>
+      <c r="AO360" t="inlineStr"/>
+      <c r="AP360" t="inlineStr"/>
+      <c r="AQ360" t="inlineStr"/>
+      <c r="AR360" t="inlineStr"/>
+      <c r="AS360" t="inlineStr"/>
+      <c r="AT360" t="inlineStr"/>
+      <c r="AU360" t="inlineStr"/>
+      <c r="AV360" t="inlineStr"/>
+      <c r="AW360" t="inlineStr"/>
+      <c r="AX360" t="inlineStr"/>
+      <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr"/>
+      <c r="BA360" t="inlineStr"/>
+      <c r="BB360" t="inlineStr"/>
+      <c r="BC360" t="inlineStr"/>
+      <c r="BD360" t="inlineStr"/>
+      <c r="BE360" t="inlineStr"/>
+      <c r="BF360" t="inlineStr"/>
+      <c r="BG360" t="inlineStr"/>
+      <c r="BH360" t="inlineStr"/>
+      <c r="BI360" t="inlineStr"/>
+      <c r="BJ360" t="inlineStr"/>
+      <c r="BK360" t="inlineStr"/>
+      <c r="BL360" t="inlineStr"/>
+      <c r="BM360" t="inlineStr"/>
+      <c r="BN360" t="inlineStr"/>
+      <c r="BO360" t="inlineStr"/>
+      <c r="BP360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>dvtwTCh3</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="n">
+        <v>45541.91666666666</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flores g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F361" t="n">
+        <v>9069</v>
+      </c>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0</v>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="K361" t="n">
+        <v>64</v>
+      </c>
+      <c r="L361" t="n">
+        <v>36</v>
+      </c>
+      <c r="M361" t="n">
+        <v>14</v>
+      </c>
+      <c r="N361" t="n">
+        <v>8</v>
+      </c>
+      <c r="O361" t="n">
+        <v>8</v>
+      </c>
+      <c r="P361" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>15</v>
+      </c>
+      <c r="R361" t="n">
+        <v>14</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="U361" t="n">
+        <v>167</v>
+      </c>
+      <c r="V361" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W361" t="n">
+        <v>0</v>
+      </c>
+      <c r="X361" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA361" t="inlineStr"/>
+      <c r="AB361" t="inlineStr"/>
+      <c r="AC361" t="inlineStr"/>
+      <c r="AD361" t="inlineStr"/>
+      <c r="AE361" t="inlineStr"/>
+      <c r="AF361" t="inlineStr"/>
+      <c r="AG361" t="inlineStr"/>
+      <c r="AH361" t="inlineStr"/>
+      <c r="AI361" t="inlineStr"/>
+      <c r="AJ361" t="inlineStr"/>
+      <c r="AK361" t="inlineStr"/>
+      <c r="AL361" t="inlineStr"/>
+      <c r="AM361" t="inlineStr"/>
+      <c r="AN361" t="inlineStr"/>
+      <c r="AO361" t="inlineStr"/>
+      <c r="AP361" t="inlineStr"/>
+      <c r="AQ361" t="inlineStr"/>
+      <c r="AR361" t="inlineStr"/>
+      <c r="AS361" t="inlineStr"/>
+      <c r="AT361" t="inlineStr"/>
+      <c r="AU361" t="inlineStr"/>
+      <c r="AV361" t="inlineStr"/>
+      <c r="AW361" t="inlineStr"/>
+      <c r="AX361" t="inlineStr"/>
+      <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr"/>
+      <c r="BA361" t="inlineStr"/>
+      <c r="BB361" t="inlineStr"/>
+      <c r="BC361" t="inlineStr"/>
+      <c r="BD361" t="inlineStr"/>
+      <c r="BE361" t="inlineStr"/>
+      <c r="BF361" t="inlineStr"/>
+      <c r="BG361" t="inlineStr"/>
+      <c r="BH361" t="inlineStr"/>
+      <c r="BI361" t="inlineStr"/>
+      <c r="BJ361" t="inlineStr"/>
+      <c r="BK361" t="inlineStr"/>
+      <c r="BL361" t="inlineStr"/>
+      <c r="BM361" t="inlineStr"/>
+      <c r="BN361" t="inlineStr"/>
+      <c r="BO361" t="inlineStr"/>
+      <c r="BP361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>ryxZThwc</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="n">
+        <v>45541.85416666666</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">montero r 
+  cos </t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lynn family stadium
+  louisville  ky </t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>15304</v>
+      </c>
+      <c r="F362" t="n">
+        <v>8207</v>
+      </c>
+      <c r="G362" t="n">
+        <v>1</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0</v>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="K362" t="n">
+        <v>48</v>
+      </c>
+      <c r="L362" t="n">
+        <v>52</v>
+      </c>
+      <c r="M362" t="n">
+        <v>12</v>
+      </c>
+      <c r="N362" t="n">
+        <v>6</v>
+      </c>
+      <c r="O362" t="n">
+        <v>4</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>21</v>
+      </c>
+      <c r="R362" t="n">
+        <v>11</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="U362" t="n">
+        <v>167</v>
+      </c>
+      <c r="V362" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W362" t="n">
+        <v>0</v>
+      </c>
+      <c r="X362" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA362" t="inlineStr"/>
+      <c r="AB362" t="inlineStr"/>
+      <c r="AC362" t="inlineStr"/>
+      <c r="AD362" t="inlineStr"/>
+      <c r="AE362" t="inlineStr"/>
+      <c r="AF362" t="inlineStr"/>
+      <c r="AG362" t="inlineStr"/>
+      <c r="AH362" t="inlineStr"/>
+      <c r="AI362" t="inlineStr"/>
+      <c r="AJ362" t="inlineStr"/>
+      <c r="AK362" t="inlineStr"/>
+      <c r="AL362" t="inlineStr"/>
+      <c r="AM362" t="inlineStr"/>
+      <c r="AN362" t="inlineStr"/>
+      <c r="AO362" t="inlineStr"/>
+      <c r="AP362" t="inlineStr"/>
+      <c r="AQ362" t="inlineStr"/>
+      <c r="AR362" t="inlineStr"/>
+      <c r="AS362" t="inlineStr"/>
+      <c r="AT362" t="inlineStr"/>
+      <c r="AU362" t="inlineStr"/>
+      <c r="AV362" t="inlineStr"/>
+      <c r="AW362" t="inlineStr"/>
+      <c r="AX362" t="inlineStr"/>
+      <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr"/>
+      <c r="BA362" t="inlineStr"/>
+      <c r="BB362" t="inlineStr"/>
+      <c r="BC362" t="inlineStr"/>
+      <c r="BD362" t="inlineStr"/>
+      <c r="BE362" t="inlineStr"/>
+      <c r="BF362" t="inlineStr"/>
+      <c r="BG362" t="inlineStr"/>
+      <c r="BH362" t="inlineStr"/>
+      <c r="BI362" t="inlineStr"/>
+      <c r="BJ362" t="inlineStr"/>
+      <c r="BK362" t="inlineStr"/>
+      <c r="BL362" t="inlineStr"/>
+      <c r="BM362" t="inlineStr"/>
+      <c r="BN362" t="inlineStr"/>
+      <c r="BO362" t="inlineStr"/>
+      <c r="BP362" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP362"/>
+  <dimension ref="A1:BP365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63959,6 +63959,432 @@
       <c r="BO362" t="inlineStr"/>
       <c r="BP362" t="inlineStr"/>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>WdfLujx9</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="n">
+        <v>45546.89583333334</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oneok field
+  tulsa  ok </t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>7833</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2663</v>
+      </c>
+      <c r="G363" t="n">
+        <v>1</v>
+      </c>
+      <c r="H363" t="n">
+        <v>1</v>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="K363" t="n">
+        <v>39</v>
+      </c>
+      <c r="L363" t="n">
+        <v>61</v>
+      </c>
+      <c r="M363" t="n">
+        <v>9</v>
+      </c>
+      <c r="N363" t="n">
+        <v>9</v>
+      </c>
+      <c r="O363" t="n">
+        <v>2</v>
+      </c>
+      <c r="P363" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>18</v>
+      </c>
+      <c r="R363" t="n">
+        <v>10</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="U363" t="n">
+        <v>167</v>
+      </c>
+      <c r="V363" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W363" t="n">
+        <v>0</v>
+      </c>
+      <c r="X363" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA363" t="inlineStr"/>
+      <c r="AB363" t="inlineStr"/>
+      <c r="AC363" t="inlineStr"/>
+      <c r="AD363" t="inlineStr"/>
+      <c r="AE363" t="inlineStr"/>
+      <c r="AF363" t="inlineStr"/>
+      <c r="AG363" t="inlineStr"/>
+      <c r="AH363" t="inlineStr"/>
+      <c r="AI363" t="inlineStr"/>
+      <c r="AJ363" t="inlineStr"/>
+      <c r="AK363" t="inlineStr"/>
+      <c r="AL363" t="inlineStr"/>
+      <c r="AM363" t="inlineStr"/>
+      <c r="AN363" t="inlineStr"/>
+      <c r="AO363" t="inlineStr"/>
+      <c r="AP363" t="inlineStr"/>
+      <c r="AQ363" t="inlineStr"/>
+      <c r="AR363" t="inlineStr"/>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="inlineStr"/>
+      <c r="AU363" t="inlineStr"/>
+      <c r="AV363" t="inlineStr"/>
+      <c r="AW363" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AX363" t="n">
+        <v>185</v>
+      </c>
+      <c r="AY363" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ363" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="BA363" t="n">
+        <v>415000</v>
+      </c>
+      <c r="BB363" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="BC363" t="inlineStr"/>
+      <c r="BD363" t="inlineStr"/>
+      <c r="BE363" t="inlineStr"/>
+      <c r="BF363" t="inlineStr"/>
+      <c r="BG363" t="inlineStr"/>
+      <c r="BH363" t="inlineStr"/>
+      <c r="BI363" t="inlineStr"/>
+      <c r="BJ363" t="inlineStr"/>
+      <c r="BK363" t="inlineStr"/>
+      <c r="BL363" t="inlineStr"/>
+      <c r="BM363" t="inlineStr"/>
+      <c r="BN363" t="inlineStr"/>
+      <c r="BO363" t="inlineStr"/>
+      <c r="BP363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>h6eHtWM2</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="n">
+        <v>45546.875</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez l 
+  usa </t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">protective stadium
+  birmingham  al </t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>47100</v>
+      </c>
+      <c r="F364" t="n">
+        <v>5058</v>
+      </c>
+      <c r="G364" t="n">
+        <v>2</v>
+      </c>
+      <c r="H364" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>AohGC74A</t>
+        </is>
+      </c>
+      <c r="K364" t="n">
+        <v>50</v>
+      </c>
+      <c r="L364" t="n">
+        <v>50</v>
+      </c>
+      <c r="M364" t="n">
+        <v>9</v>
+      </c>
+      <c r="N364" t="n">
+        <v>23</v>
+      </c>
+      <c r="O364" t="n">
+        <v>5</v>
+      </c>
+      <c r="P364" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>16</v>
+      </c>
+      <c r="R364" t="n">
+        <v>12</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>r7lXig46</t>
+        </is>
+      </c>
+      <c r="U364" t="n">
+        <v>167</v>
+      </c>
+      <c r="V364" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W364" t="n">
+        <v>0</v>
+      </c>
+      <c r="X364" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA364" t="inlineStr"/>
+      <c r="AB364" t="inlineStr"/>
+      <c r="AC364" t="inlineStr"/>
+      <c r="AD364" t="inlineStr"/>
+      <c r="AE364" t="inlineStr"/>
+      <c r="AF364" t="inlineStr"/>
+      <c r="AG364" t="inlineStr"/>
+      <c r="AH364" t="inlineStr"/>
+      <c r="AI364" t="inlineStr"/>
+      <c r="AJ364" t="inlineStr"/>
+      <c r="AK364" t="inlineStr"/>
+      <c r="AL364" t="inlineStr"/>
+      <c r="AM364" t="inlineStr"/>
+      <c r="AN364" t="inlineStr"/>
+      <c r="AO364" t="inlineStr"/>
+      <c r="AP364" t="inlineStr"/>
+      <c r="AQ364" t="inlineStr"/>
+      <c r="AR364" t="inlineStr"/>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="inlineStr"/>
+      <c r="AU364" t="inlineStr"/>
+      <c r="AV364" t="inlineStr"/>
+      <c r="AW364" t="inlineStr"/>
+      <c r="AX364" t="inlineStr"/>
+      <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr"/>
+      <c r="BA364" t="inlineStr"/>
+      <c r="BB364" t="inlineStr"/>
+      <c r="BC364" t="inlineStr"/>
+      <c r="BD364" t="inlineStr"/>
+      <c r="BE364" t="inlineStr"/>
+      <c r="BF364" t="inlineStr"/>
+      <c r="BG364" t="inlineStr"/>
+      <c r="BH364" t="inlineStr"/>
+      <c r="BI364" t="inlineStr"/>
+      <c r="BJ364" t="inlineStr"/>
+      <c r="BK364" t="inlineStr"/>
+      <c r="BL364" t="inlineStr"/>
+      <c r="BM364" t="inlineStr"/>
+      <c r="BN364" t="inlineStr"/>
+      <c r="BO364" t="inlineStr"/>
+      <c r="BP364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>QJgPvAiF</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="n">
+        <v>45546.875</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmanovic e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">autozone park
+  memphis  tn </t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F365" t="n">
+        <v>3013</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Ew2P6PKC</t>
+        </is>
+      </c>
+      <c r="K365" t="n">
+        <v>58</v>
+      </c>
+      <c r="L365" t="n">
+        <v>42</v>
+      </c>
+      <c r="M365" t="n">
+        <v>29</v>
+      </c>
+      <c r="N365" t="n">
+        <v>8</v>
+      </c>
+      <c r="O365" t="n">
+        <v>7</v>
+      </c>
+      <c r="P365" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>12</v>
+      </c>
+      <c r="R365" t="n">
+        <v>19</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>xYHj0Fat</t>
+        </is>
+      </c>
+      <c r="U365" t="n">
+        <v>167</v>
+      </c>
+      <c r="V365" t="n">
+        <v>1673</v>
+      </c>
+      <c r="W365" t="n">
+        <v>0</v>
+      </c>
+      <c r="X365" t="n">
+        <v>2024</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA365" t="inlineStr"/>
+      <c r="AB365" t="inlineStr"/>
+      <c r="AC365" t="inlineStr"/>
+      <c r="AD365" t="inlineStr"/>
+      <c r="AE365" t="inlineStr"/>
+      <c r="AF365" t="inlineStr"/>
+      <c r="AG365" t="inlineStr"/>
+      <c r="AH365" t="inlineStr"/>
+      <c r="AI365" t="inlineStr"/>
+      <c r="AJ365" t="inlineStr"/>
+      <c r="AK365" t="inlineStr"/>
+      <c r="AL365" t="inlineStr"/>
+      <c r="AM365" t="inlineStr"/>
+      <c r="AN365" t="inlineStr"/>
+      <c r="AO365" t="inlineStr"/>
+      <c r="AP365" t="inlineStr"/>
+      <c r="AQ365" t="inlineStr"/>
+      <c r="AR365" t="inlineStr"/>
+      <c r="AS365" t="inlineStr"/>
+      <c r="AT365" t="inlineStr"/>
+      <c r="AU365" t="inlineStr"/>
+      <c r="AV365" t="inlineStr"/>
+      <c r="AW365" t="inlineStr"/>
+      <c r="AX365" t="inlineStr"/>
+      <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr"/>
+      <c r="BA365" t="inlineStr"/>
+      <c r="BB365" t="inlineStr"/>
+      <c r="BC365" t="inlineStr"/>
+      <c r="BD365" t="inlineStr"/>
+      <c r="BE365" t="inlineStr"/>
+      <c r="BF365" t="inlineStr"/>
+      <c r="BG365" t="inlineStr"/>
+      <c r="BH365" t="inlineStr"/>
+      <c r="BI365" t="inlineStr"/>
+      <c r="BJ365" t="inlineStr"/>
+      <c r="BK365" t="inlineStr"/>
+      <c r="BL365" t="inlineStr"/>
+      <c r="BM365" t="inlineStr"/>
+      <c r="BN365" t="inlineStr"/>
+      <c r="BO365" t="inlineStr"/>
+      <c r="BP365" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/data/usa/p6_deployment/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL391"/>
+  <dimension ref="A1:CL405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93833,6 +93833,3684 @@
       <c r="CK391" t="inlineStr"/>
       <c r="CL391" t="inlineStr"/>
     </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>xhnHdYtb</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="n">
+        <v>45553.97916666666</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F392" t="n">
+        <v>22153</v>
+      </c>
+      <c r="G392" t="n">
+        <v>1</v>
+      </c>
+      <c r="H392" t="n">
+        <v>1</v>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="K392" t="n">
+        <v>60</v>
+      </c>
+      <c r="L392" t="n">
+        <v>40</v>
+      </c>
+      <c r="M392" t="n">
+        <v>15</v>
+      </c>
+      <c r="N392" t="n">
+        <v>10</v>
+      </c>
+      <c r="O392" t="n">
+        <v>7</v>
+      </c>
+      <c r="P392" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>7</v>
+      </c>
+      <c r="R392" t="n">
+        <v>4</v>
+      </c>
+      <c r="S392" t="n">
+        <v>1</v>
+      </c>
+      <c r="T392" t="n">
+        <v>3</v>
+      </c>
+      <c r="U392" t="n">
+        <v>18</v>
+      </c>
+      <c r="V392" t="n">
+        <v>15</v>
+      </c>
+      <c r="W392" t="n">
+        <v>5</v>
+      </c>
+      <c r="X392" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA392" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB392" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC392" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD392" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF392" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG392" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH392" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI392" t="n">
+        <v>650</v>
+      </c>
+      <c r="AJ392" t="n">
+        <v>421</v>
+      </c>
+      <c r="AK392" t="n">
+        <v>578</v>
+      </c>
+      <c r="AL392" t="n">
+        <v>345</v>
+      </c>
+      <c r="AM392" t="n">
+        <v>172</v>
+      </c>
+      <c r="AN392" t="n">
+        <v>91</v>
+      </c>
+      <c r="AO392" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP392" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ392" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR392" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS392" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT392" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU392" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="AV392" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="AW392" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX392" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ392" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA392" t="inlineStr"/>
+      <c r="BB392" t="inlineStr"/>
+      <c r="BC392" t="inlineStr"/>
+      <c r="BD392" t="inlineStr"/>
+      <c r="BE392" t="inlineStr"/>
+      <c r="BF392" t="inlineStr"/>
+      <c r="BG392" t="inlineStr"/>
+      <c r="BH392" t="inlineStr"/>
+      <c r="BI392" t="inlineStr"/>
+      <c r="BJ392" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="BK392" t="n">
+        <v>28.45454545454545</v>
+      </c>
+      <c r="BL392" t="n">
+        <v>180.3636363636364</v>
+      </c>
+      <c r="BM392" t="n">
+        <v>72.81818181818181</v>
+      </c>
+      <c r="BN392" t="inlineStr"/>
+      <c r="BO392" t="n">
+        <v>27.88888888888889</v>
+      </c>
+      <c r="BP392" t="n">
+        <v>179.8888888888889</v>
+      </c>
+      <c r="BQ392" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="BR392" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BS392" t="n">
+        <v>25.90476190476191</v>
+      </c>
+      <c r="BT392" t="n">
+        <v>181</v>
+      </c>
+      <c r="BU392" t="n">
+        <v>68.04761904761905</v>
+      </c>
+      <c r="BV392" t="inlineStr"/>
+      <c r="BW392" t="n">
+        <v>27.10526315789474</v>
+      </c>
+      <c r="BX392" t="n">
+        <v>182.0526315789474</v>
+      </c>
+      <c r="BY392" t="n">
+        <v>64.94736842105263</v>
+      </c>
+      <c r="BZ392" t="inlineStr"/>
+      <c r="CA392" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="CB392" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="CC392" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="CD392" t="inlineStr"/>
+      <c r="CE392" t="n">
+        <v>4</v>
+      </c>
+      <c r="CF392" t="n">
+        <v>270</v>
+      </c>
+      <c r="CG392" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="CH392" t="n">
+        <v>180.25</v>
+      </c>
+      <c r="CI392" t="n">
+        <v>66</v>
+      </c>
+      <c r="CJ392" t="n">
+        <v>4000</v>
+      </c>
+      <c r="CK392" t="n">
+        <v>4</v>
+      </c>
+      <c r="CL392" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>GroLehd4</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="n">
+        <v>45553.97916666666</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="n">
+        <v>4</v>
+      </c>
+      <c r="H393" t="n">
+        <v>2</v>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="K393" t="n">
+        <v>43</v>
+      </c>
+      <c r="L393" t="n">
+        <v>57</v>
+      </c>
+      <c r="M393" t="n">
+        <v>22</v>
+      </c>
+      <c r="N393" t="n">
+        <v>25</v>
+      </c>
+      <c r="O393" t="n">
+        <v>12</v>
+      </c>
+      <c r="P393" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>8</v>
+      </c>
+      <c r="R393" t="n">
+        <v>10</v>
+      </c>
+      <c r="S393" t="n">
+        <v>2</v>
+      </c>
+      <c r="T393" t="n">
+        <v>7</v>
+      </c>
+      <c r="U393" t="n">
+        <v>11</v>
+      </c>
+      <c r="V393" t="n">
+        <v>9</v>
+      </c>
+      <c r="W393" t="n">
+        <v>5</v>
+      </c>
+      <c r="X393" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA393" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB393" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC393" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD393" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE393" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF393" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG393" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH393" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI393" t="n">
+        <v>443</v>
+      </c>
+      <c r="AJ393" t="n">
+        <v>736</v>
+      </c>
+      <c r="AK393" t="n">
+        <v>388</v>
+      </c>
+      <c r="AL393" t="n">
+        <v>649</v>
+      </c>
+      <c r="AM393" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN393" t="n">
+        <v>174</v>
+      </c>
+      <c r="AO393" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP393" t="n">
+        <v>94</v>
+      </c>
+      <c r="AQ393" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR393" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS393" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU393" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="AV393" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="AW393" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX393" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY393" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ393" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA393" t="inlineStr"/>
+      <c r="BB393" t="inlineStr"/>
+      <c r="BC393" t="inlineStr"/>
+      <c r="BD393" t="inlineStr"/>
+      <c r="BE393" t="inlineStr"/>
+      <c r="BF393" t="inlineStr"/>
+      <c r="BG393" t="inlineStr"/>
+      <c r="BH393" t="inlineStr"/>
+      <c r="BI393" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="BJ393" t="inlineStr"/>
+      <c r="BK393" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BL393" t="n">
+        <v>178</v>
+      </c>
+      <c r="BM393" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="BN393" t="n">
+        <v>4300</v>
+      </c>
+      <c r="BO393" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="BP393" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="BQ393" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BR393" t="n">
+        <v>5300</v>
+      </c>
+      <c r="BS393" t="n">
+        <v>25.10526315789474</v>
+      </c>
+      <c r="BT393" t="n">
+        <v>180.7894736842105</v>
+      </c>
+      <c r="BU393" t="n">
+        <v>67.15789473684211</v>
+      </c>
+      <c r="BV393" t="n">
+        <v>2947.368421052632</v>
+      </c>
+      <c r="BW393" t="n">
+        <v>24.77272727272727</v>
+      </c>
+      <c r="BX393" t="n">
+        <v>179.2727272727273</v>
+      </c>
+      <c r="BY393" t="n">
+        <v>67.77272727272727</v>
+      </c>
+      <c r="BZ393" t="inlineStr"/>
+      <c r="CA393" t="n">
+        <v>26</v>
+      </c>
+      <c r="CB393" t="n">
+        <v>170</v>
+      </c>
+      <c r="CC393" t="n">
+        <v>70</v>
+      </c>
+      <c r="CD393" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CE393" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF393" t="n">
+        <v>70</v>
+      </c>
+      <c r="CG393" t="n">
+        <v>26</v>
+      </c>
+      <c r="CH393" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="CI393" t="n">
+        <v>68</v>
+      </c>
+      <c r="CJ393" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="CK393" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL393" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>YJuQfCBA</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="n">
+        <v>45553.97916666666</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F394" t="n">
+        <v>29326</v>
+      </c>
+      <c r="G394" t="n">
+        <v>2</v>
+      </c>
+      <c r="H394" t="n">
+        <v>2</v>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="K394" t="n">
+        <v>49</v>
+      </c>
+      <c r="L394" t="n">
+        <v>51</v>
+      </c>
+      <c r="M394" t="n">
+        <v>19</v>
+      </c>
+      <c r="N394" t="n">
+        <v>9</v>
+      </c>
+      <c r="O394" t="n">
+        <v>4</v>
+      </c>
+      <c r="P394" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>9</v>
+      </c>
+      <c r="R394" t="n">
+        <v>3</v>
+      </c>
+      <c r="S394" t="n">
+        <v>6</v>
+      </c>
+      <c r="T394" t="n">
+        <v>3</v>
+      </c>
+      <c r="U394" t="n">
+        <v>15</v>
+      </c>
+      <c r="V394" t="n">
+        <v>11</v>
+      </c>
+      <c r="W394" t="n">
+        <v>5</v>
+      </c>
+      <c r="X394" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA394" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB394" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF394" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH394" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI394" t="n">
+        <v>481</v>
+      </c>
+      <c r="AJ394" t="n">
+        <v>602</v>
+      </c>
+      <c r="AK394" t="n">
+        <v>409</v>
+      </c>
+      <c r="AL394" t="n">
+        <v>518</v>
+      </c>
+      <c r="AM394" t="n">
+        <v>115</v>
+      </c>
+      <c r="AN394" t="n">
+        <v>102</v>
+      </c>
+      <c r="AO394" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP394" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR394" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="AV394" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="AW394" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX394" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY394" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ394" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA394" t="inlineStr"/>
+      <c r="BB394" t="inlineStr"/>
+      <c r="BC394" t="inlineStr"/>
+      <c r="BD394" t="inlineStr"/>
+      <c r="BE394" t="inlineStr"/>
+      <c r="BF394" t="inlineStr"/>
+      <c r="BG394" t="inlineStr"/>
+      <c r="BH394" t="inlineStr"/>
+      <c r="BI394" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="BJ394" t="inlineStr"/>
+      <c r="BK394" t="n">
+        <v>26.77777777777778</v>
+      </c>
+      <c r="BL394" t="n">
+        <v>179.5555555555555</v>
+      </c>
+      <c r="BM394" t="n">
+        <v>70</v>
+      </c>
+      <c r="BN394" t="inlineStr"/>
+      <c r="BO394" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="BP394" t="n">
+        <v>178.4444444444445</v>
+      </c>
+      <c r="BQ394" t="n">
+        <v>68</v>
+      </c>
+      <c r="BR394" t="inlineStr"/>
+      <c r="BS394" t="n">
+        <v>21.94444444444444</v>
+      </c>
+      <c r="BT394" t="n">
+        <v>179.4444444444445</v>
+      </c>
+      <c r="BU394" t="n">
+        <v>64.27777777777777</v>
+      </c>
+      <c r="BV394" t="inlineStr"/>
+      <c r="BW394" t="n">
+        <v>26.91304347826087</v>
+      </c>
+      <c r="BX394" t="n">
+        <v>179.4347826086957</v>
+      </c>
+      <c r="BY394" t="n">
+        <v>67.04347826086956</v>
+      </c>
+      <c r="BZ394" t="inlineStr"/>
+      <c r="CA394" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="CB394" t="n">
+        <v>175.6666666666667</v>
+      </c>
+      <c r="CC394" t="n">
+        <v>67</v>
+      </c>
+      <c r="CD394" t="inlineStr"/>
+      <c r="CE394" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF394" t="n">
+        <v>201</v>
+      </c>
+      <c r="CG394" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="CH394" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="CI394" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="CJ394" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="CK394" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL394" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>rVnDcERi</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="n">
+        <v>45553.9375</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F395" t="n">
+        <v>19436</v>
+      </c>
+      <c r="G395" t="n">
+        <v>3</v>
+      </c>
+      <c r="H395" t="n">
+        <v>2</v>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="K395" t="n">
+        <v>51</v>
+      </c>
+      <c r="L395" t="n">
+        <v>49</v>
+      </c>
+      <c r="M395" t="n">
+        <v>13</v>
+      </c>
+      <c r="N395" t="n">
+        <v>17</v>
+      </c>
+      <c r="O395" t="n">
+        <v>8</v>
+      </c>
+      <c r="P395" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>5</v>
+      </c>
+      <c r="R395" t="n">
+        <v>4</v>
+      </c>
+      <c r="S395" t="n">
+        <v>0</v>
+      </c>
+      <c r="T395" t="n">
+        <v>7</v>
+      </c>
+      <c r="U395" t="n">
+        <v>14</v>
+      </c>
+      <c r="V395" t="n">
+        <v>14</v>
+      </c>
+      <c r="W395" t="n">
+        <v>2</v>
+      </c>
+      <c r="X395" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y395" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC395" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD395" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF395" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG395" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH395" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI395" t="n">
+        <v>475</v>
+      </c>
+      <c r="AJ395" t="n">
+        <v>563</v>
+      </c>
+      <c r="AK395" t="n">
+        <v>378</v>
+      </c>
+      <c r="AL395" t="n">
+        <v>439</v>
+      </c>
+      <c r="AM395" t="inlineStr"/>
+      <c r="AN395" t="inlineStr"/>
+      <c r="AO395" t="inlineStr"/>
+      <c r="AP395" t="inlineStr"/>
+      <c r="AQ395" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR395" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS395" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT395" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="AV395" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="AW395" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX395" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY395" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ395" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA395" t="inlineStr"/>
+      <c r="BB395" t="inlineStr"/>
+      <c r="BC395" t="inlineStr"/>
+      <c r="BD395" t="inlineStr"/>
+      <c r="BE395" t="inlineStr"/>
+      <c r="BF395" t="inlineStr"/>
+      <c r="BG395" t="inlineStr"/>
+      <c r="BH395" t="inlineStr"/>
+      <c r="BI395" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="BJ395" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="BK395" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="BL395" t="n">
+        <v>182.8888888888889</v>
+      </c>
+      <c r="BM395" t="n">
+        <v>64.88888888888889</v>
+      </c>
+      <c r="BN395" t="inlineStr"/>
+      <c r="BO395" t="n">
+        <v>27</v>
+      </c>
+      <c r="BP395" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BQ395" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BR395" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BS395" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT395" t="n">
+        <v>178.6363636363636</v>
+      </c>
+      <c r="BU395" t="n">
+        <v>64.54545454545455</v>
+      </c>
+      <c r="BV395" t="n">
+        <v>3363.636363636364</v>
+      </c>
+      <c r="BW395" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX395" t="n">
+        <v>177.8421052631579</v>
+      </c>
+      <c r="BY395" t="n">
+        <v>64.94736842105263</v>
+      </c>
+      <c r="BZ395" t="inlineStr"/>
+      <c r="CA395" t="n">
+        <v>27</v>
+      </c>
+      <c r="CB395" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="CC395" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="CD395" t="n">
+        <v>4200</v>
+      </c>
+      <c r="CE395" t="n">
+        <v>5</v>
+      </c>
+      <c r="CF395" t="n">
+        <v>341</v>
+      </c>
+      <c r="CG395" t="n">
+        <v>23</v>
+      </c>
+      <c r="CH395" t="n">
+        <v>180</v>
+      </c>
+      <c r="CI395" t="n">
+        <v>65</v>
+      </c>
+      <c r="CJ395" t="n">
+        <v>2333.333333333333</v>
+      </c>
+      <c r="CK395" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL395" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>0n3Ddmal</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F396" t="n">
+        <v>14282</v>
+      </c>
+      <c r="G396" t="n">
+        <v>1</v>
+      </c>
+      <c r="H396" t="n">
+        <v>1</v>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="K396" t="n">
+        <v>62</v>
+      </c>
+      <c r="L396" t="n">
+        <v>38</v>
+      </c>
+      <c r="M396" t="n">
+        <v>10</v>
+      </c>
+      <c r="N396" t="n">
+        <v>8</v>
+      </c>
+      <c r="O396" t="n">
+        <v>2</v>
+      </c>
+      <c r="P396" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>2</v>
+      </c>
+      <c r="R396" t="n">
+        <v>2</v>
+      </c>
+      <c r="S396" t="n">
+        <v>6</v>
+      </c>
+      <c r="T396" t="n">
+        <v>2</v>
+      </c>
+      <c r="U396" t="n">
+        <v>13</v>
+      </c>
+      <c r="V396" t="n">
+        <v>22</v>
+      </c>
+      <c r="W396" t="n">
+        <v>13</v>
+      </c>
+      <c r="X396" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y396" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA396" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB396" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC396" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF396" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG396" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH396" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI396" t="n">
+        <v>722</v>
+      </c>
+      <c r="AJ396" t="n">
+        <v>357</v>
+      </c>
+      <c r="AK396" t="n">
+        <v>644</v>
+      </c>
+      <c r="AL396" t="n">
+        <v>286</v>
+      </c>
+      <c r="AM396" t="n">
+        <v>54</v>
+      </c>
+      <c r="AN396" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO396" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP396" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ396" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR396" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU396" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="AV396" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="AW396" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX396" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY396" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ396" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA396" t="inlineStr"/>
+      <c r="BB396" t="inlineStr"/>
+      <c r="BC396" t="inlineStr"/>
+      <c r="BD396" t="inlineStr"/>
+      <c r="BE396" t="inlineStr"/>
+      <c r="BF396" t="inlineStr"/>
+      <c r="BG396" t="inlineStr"/>
+      <c r="BH396" t="inlineStr"/>
+      <c r="BI396" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="BJ396" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="BK396" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="BL396" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="BM396" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="BN396" t="n">
+        <v>3500</v>
+      </c>
+      <c r="BO396" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="BP396" t="n">
+        <v>176.3636363636364</v>
+      </c>
+      <c r="BQ396" t="n">
+        <v>69.18181818181819</v>
+      </c>
+      <c r="BR396" t="n">
+        <v>4363.636363636364</v>
+      </c>
+      <c r="BS396" t="n">
+        <v>25.40909090909091</v>
+      </c>
+      <c r="BT396" t="n">
+        <v>178.1818181818182</v>
+      </c>
+      <c r="BU396" t="n">
+        <v>64.36363636363636</v>
+      </c>
+      <c r="BV396" t="inlineStr"/>
+      <c r="BW396" t="n">
+        <v>24.70588235294118</v>
+      </c>
+      <c r="BX396" t="n">
+        <v>177.8823529411765</v>
+      </c>
+      <c r="BY396" t="n">
+        <v>65.82352941176471</v>
+      </c>
+      <c r="BZ396" t="inlineStr"/>
+      <c r="CA396" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="CB396" t="n">
+        <v>184</v>
+      </c>
+      <c r="CC396" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="CD396" t="inlineStr"/>
+      <c r="CE396" t="n">
+        <v>4</v>
+      </c>
+      <c r="CF396" t="n">
+        <v>246</v>
+      </c>
+      <c r="CG396" t="n">
+        <v>22</v>
+      </c>
+      <c r="CH396" t="n">
+        <v>180</v>
+      </c>
+      <c r="CI396" t="n">
+        <v>62</v>
+      </c>
+      <c r="CJ396" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CK396" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL396" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>SM4QZAZp</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F397" t="n">
+        <v>19649</v>
+      </c>
+      <c r="G397" t="n">
+        <v>1</v>
+      </c>
+      <c r="H397" t="n">
+        <v>2</v>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="K397" t="n">
+        <v>46</v>
+      </c>
+      <c r="L397" t="n">
+        <v>54</v>
+      </c>
+      <c r="M397" t="n">
+        <v>11</v>
+      </c>
+      <c r="N397" t="n">
+        <v>12</v>
+      </c>
+      <c r="O397" t="n">
+        <v>5</v>
+      </c>
+      <c r="P397" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>4</v>
+      </c>
+      <c r="R397" t="n">
+        <v>4</v>
+      </c>
+      <c r="S397" t="n">
+        <v>2</v>
+      </c>
+      <c r="T397" t="n">
+        <v>1</v>
+      </c>
+      <c r="U397" t="n">
+        <v>16</v>
+      </c>
+      <c r="V397" t="n">
+        <v>15</v>
+      </c>
+      <c r="W397" t="n">
+        <v>7</v>
+      </c>
+      <c r="X397" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB397" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC397" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD397" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF397" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG397" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH397" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI397" t="n">
+        <v>449</v>
+      </c>
+      <c r="AJ397" t="n">
+        <v>531</v>
+      </c>
+      <c r="AK397" t="n">
+        <v>360</v>
+      </c>
+      <c r="AL397" t="n">
+        <v>448</v>
+      </c>
+      <c r="AM397" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN397" t="n">
+        <v>118</v>
+      </c>
+      <c r="AO397" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP397" t="n">
+        <v>33</v>
+      </c>
+      <c r="AQ397" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR397" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS397" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT397" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU397" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="AV397" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="AW397" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX397" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ397" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA397" t="inlineStr"/>
+      <c r="BB397" t="inlineStr"/>
+      <c r="BC397" t="inlineStr"/>
+      <c r="BD397" t="inlineStr"/>
+      <c r="BE397" t="inlineStr"/>
+      <c r="BF397" t="inlineStr"/>
+      <c r="BG397" t="inlineStr"/>
+      <c r="BH397" t="inlineStr"/>
+      <c r="BI397" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="BJ397" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="BK397" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BL397" t="n">
+        <v>183</v>
+      </c>
+      <c r="BM397" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="BN397" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BO397" t="n">
+        <v>25</v>
+      </c>
+      <c r="BP397" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="BQ397" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BR397" t="inlineStr"/>
+      <c r="BS397" t="n">
+        <v>26.26086956521739</v>
+      </c>
+      <c r="BT397" t="n">
+        <v>178.2173913043478</v>
+      </c>
+      <c r="BU397" t="n">
+        <v>66.1304347826087</v>
+      </c>
+      <c r="BV397" t="inlineStr"/>
+      <c r="BW397" t="n">
+        <v>25.45833333333333</v>
+      </c>
+      <c r="BX397" t="n">
+        <v>180.625</v>
+      </c>
+      <c r="BY397" t="n">
+        <v>64.04166666666667</v>
+      </c>
+      <c r="BZ397" t="inlineStr"/>
+      <c r="CA397" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="CB397" t="n">
+        <v>187</v>
+      </c>
+      <c r="CC397" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="CD397" t="n">
+        <v>1500</v>
+      </c>
+      <c r="CE397" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF397" t="n">
+        <v>127</v>
+      </c>
+      <c r="CG397" t="n">
+        <v>27</v>
+      </c>
+      <c r="CH397" t="n">
+        <v>186</v>
+      </c>
+      <c r="CI397" t="n">
+        <v>61.66666666666666</v>
+      </c>
+      <c r="CJ397" t="inlineStr"/>
+      <c r="CK397" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL397" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>URr9bfCo</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F398" t="n">
+        <v>27967</v>
+      </c>
+      <c r="G398" t="n">
+        <v>1</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="K398" t="n">
+        <v>44</v>
+      </c>
+      <c r="L398" t="n">
+        <v>56</v>
+      </c>
+      <c r="M398" t="n">
+        <v>5</v>
+      </c>
+      <c r="N398" t="n">
+        <v>9</v>
+      </c>
+      <c r="O398" t="n">
+        <v>2</v>
+      </c>
+      <c r="P398" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>1</v>
+      </c>
+      <c r="R398" t="n">
+        <v>4</v>
+      </c>
+      <c r="S398" t="n">
+        <v>2</v>
+      </c>
+      <c r="T398" t="n">
+        <v>2</v>
+      </c>
+      <c r="U398" t="n">
+        <v>17</v>
+      </c>
+      <c r="V398" t="n">
+        <v>14</v>
+      </c>
+      <c r="W398" t="n">
+        <v>1</v>
+      </c>
+      <c r="X398" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y398" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB398" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD398" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF398" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG398" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH398" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI398" t="n">
+        <v>468</v>
+      </c>
+      <c r="AJ398" t="n">
+        <v>696</v>
+      </c>
+      <c r="AK398" t="n">
+        <v>397</v>
+      </c>
+      <c r="AL398" t="n">
+        <v>648</v>
+      </c>
+      <c r="AM398" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN398" t="n">
+        <v>134</v>
+      </c>
+      <c r="AO398" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP398" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ398" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT398" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU398" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="AV398" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="AW398" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX398" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ398" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA398" t="inlineStr"/>
+      <c r="BB398" t="inlineStr"/>
+      <c r="BC398" t="inlineStr"/>
+      <c r="BD398" t="inlineStr"/>
+      <c r="BE398" t="inlineStr"/>
+      <c r="BF398" t="inlineStr"/>
+      <c r="BG398" t="inlineStr"/>
+      <c r="BH398" t="inlineStr"/>
+      <c r="BI398" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="BJ398" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="BK398" t="n">
+        <v>28.63636363636364</v>
+      </c>
+      <c r="BL398" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="BM398" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="BN398" t="n">
+        <v>4909.090909090909</v>
+      </c>
+      <c r="BO398" t="n">
+        <v>26.36363636363636</v>
+      </c>
+      <c r="BP398" t="n">
+        <v>183.7272727272727</v>
+      </c>
+      <c r="BQ398" t="n">
+        <v>66.63636363636364</v>
+      </c>
+      <c r="BR398" t="inlineStr"/>
+      <c r="BS398" t="n">
+        <v>26.27777777777778</v>
+      </c>
+      <c r="BT398" t="n">
+        <v>184.3888888888889</v>
+      </c>
+      <c r="BU398" t="n">
+        <v>62.94444444444444</v>
+      </c>
+      <c r="BV398" t="inlineStr"/>
+      <c r="BW398" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="BX398" t="n">
+        <v>178.4583333333333</v>
+      </c>
+      <c r="BY398" t="n">
+        <v>62.66666666666666</v>
+      </c>
+      <c r="BZ398" t="inlineStr"/>
+      <c r="CA398" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="CB398" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="CC398" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="CD398" t="n">
+        <v>3250</v>
+      </c>
+      <c r="CE398" t="n">
+        <v>4</v>
+      </c>
+      <c r="CF398" t="n">
+        <v>266</v>
+      </c>
+      <c r="CG398" t="n">
+        <v>27</v>
+      </c>
+      <c r="CH398" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="CI398" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="CJ398" t="n">
+        <v>3250</v>
+      </c>
+      <c r="CK398" t="n">
+        <v>4</v>
+      </c>
+      <c r="CL398" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>QDIbviRT</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="n">
+        <v>45553.89583333334</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F399" t="n">
+        <v>14826</v>
+      </c>
+      <c r="G399" t="n">
+        <v>4</v>
+      </c>
+      <c r="H399" t="n">
+        <v>1</v>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="K399" t="n">
+        <v>55</v>
+      </c>
+      <c r="L399" t="n">
+        <v>45</v>
+      </c>
+      <c r="M399" t="n">
+        <v>32</v>
+      </c>
+      <c r="N399" t="n">
+        <v>6</v>
+      </c>
+      <c r="O399" t="n">
+        <v>10</v>
+      </c>
+      <c r="P399" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>7</v>
+      </c>
+      <c r="R399" t="n">
+        <v>2</v>
+      </c>
+      <c r="S399" t="n">
+        <v>15</v>
+      </c>
+      <c r="T399" t="n">
+        <v>1</v>
+      </c>
+      <c r="U399" t="n">
+        <v>7</v>
+      </c>
+      <c r="V399" t="n">
+        <v>15</v>
+      </c>
+      <c r="W399" t="n">
+        <v>11</v>
+      </c>
+      <c r="X399" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB399" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD399" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF399" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI399" t="n">
+        <v>529</v>
+      </c>
+      <c r="AJ399" t="n">
+        <v>462</v>
+      </c>
+      <c r="AK399" t="n">
+        <v>417</v>
+      </c>
+      <c r="AL399" t="n">
+        <v>364</v>
+      </c>
+      <c r="AM399" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN399" t="n">
+        <v>83</v>
+      </c>
+      <c r="AO399" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP399" t="n">
+        <v>33</v>
+      </c>
+      <c r="AQ399" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR399" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS399" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU399" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="AV399" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="AW399" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX399" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ399" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA399" t="inlineStr"/>
+      <c r="BB399" t="inlineStr"/>
+      <c r="BC399" t="inlineStr"/>
+      <c r="BD399" t="inlineStr"/>
+      <c r="BE399" t="inlineStr"/>
+      <c r="BF399" t="inlineStr"/>
+      <c r="BG399" t="inlineStr"/>
+      <c r="BH399" t="inlineStr"/>
+      <c r="BI399" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="BJ399" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="BK399" t="n">
+        <v>26.72727272727273</v>
+      </c>
+      <c r="BL399" t="n">
+        <v>180.0909090909091</v>
+      </c>
+      <c r="BM399" t="n">
+        <v>64.63636363636364</v>
+      </c>
+      <c r="BN399" t="n">
+        <v>2909.090909090909</v>
+      </c>
+      <c r="BO399" t="n">
+        <v>23.88888888888889</v>
+      </c>
+      <c r="BP399" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="BQ399" t="n">
+        <v>64.11111111111111</v>
+      </c>
+      <c r="BR399" t="inlineStr"/>
+      <c r="BS399" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BT399" t="n">
+        <v>178.8333333333333</v>
+      </c>
+      <c r="BU399" t="n">
+        <v>66.125</v>
+      </c>
+      <c r="BV399" t="inlineStr"/>
+      <c r="BW399" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="BX399" t="n">
+        <v>177.2727272727273</v>
+      </c>
+      <c r="BY399" t="n">
+        <v>60.40909090909091</v>
+      </c>
+      <c r="BZ399" t="inlineStr"/>
+      <c r="CA399" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="CB399" t="n">
+        <v>187</v>
+      </c>
+      <c r="CC399" t="n">
+        <v>68</v>
+      </c>
+      <c r="CD399" t="n">
+        <v>4500</v>
+      </c>
+      <c r="CE399" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF399" t="n">
+        <v>136</v>
+      </c>
+      <c r="CG399" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="CH399" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="CI399" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="CJ399" t="inlineStr"/>
+      <c r="CK399" t="n">
+        <v>3</v>
+      </c>
+      <c r="CL399" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>ImJfuXBN</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="n">
+        <v>45553.88541666666</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F400" t="n">
+        <v>22902</v>
+      </c>
+      <c r="G400" t="n">
+        <v>2</v>
+      </c>
+      <c r="H400" t="n">
+        <v>0</v>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="K400" t="n">
+        <v>57</v>
+      </c>
+      <c r="L400" t="n">
+        <v>43</v>
+      </c>
+      <c r="M400" t="n">
+        <v>14</v>
+      </c>
+      <c r="N400" t="n">
+        <v>4</v>
+      </c>
+      <c r="O400" t="n">
+        <v>4</v>
+      </c>
+      <c r="P400" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>2</v>
+      </c>
+      <c r="R400" t="n">
+        <v>2</v>
+      </c>
+      <c r="S400" t="n">
+        <v>8</v>
+      </c>
+      <c r="T400" t="n">
+        <v>0</v>
+      </c>
+      <c r="U400" t="n">
+        <v>18</v>
+      </c>
+      <c r="V400" t="n">
+        <v>19</v>
+      </c>
+      <c r="W400" t="n">
+        <v>7</v>
+      </c>
+      <c r="X400" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y400" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z400" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA400" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB400" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC400" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD400" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF400" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG400" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH400" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI400" t="n">
+        <v>595</v>
+      </c>
+      <c r="AJ400" t="n">
+        <v>427</v>
+      </c>
+      <c r="AK400" t="n">
+        <v>508</v>
+      </c>
+      <c r="AL400" t="n">
+        <v>357</v>
+      </c>
+      <c r="AM400" t="n">
+        <v>123</v>
+      </c>
+      <c r="AN400" t="n">
+        <v>79</v>
+      </c>
+      <c r="AO400" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP400" t="n">
+        <v>44</v>
+      </c>
+      <c r="AQ400" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR400" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS400" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT400" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU400" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="AV400" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="AW400" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX400" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ400" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA400" t="inlineStr"/>
+      <c r="BB400" t="inlineStr"/>
+      <c r="BC400" t="inlineStr"/>
+      <c r="BD400" t="inlineStr"/>
+      <c r="BE400" t="inlineStr"/>
+      <c r="BF400" t="inlineStr"/>
+      <c r="BG400" t="inlineStr"/>
+      <c r="BH400" t="inlineStr"/>
+      <c r="BI400" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="BJ400" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="BK400" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BL400" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="BM400" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="BN400" t="n">
+        <v>4600</v>
+      </c>
+      <c r="BO400" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="BP400" t="n">
+        <v>181.0909090909091</v>
+      </c>
+      <c r="BQ400" t="n">
+        <v>68.18181818181819</v>
+      </c>
+      <c r="BR400" t="n">
+        <v>8090.909090909091</v>
+      </c>
+      <c r="BS400" t="n">
+        <v>27.19047619047619</v>
+      </c>
+      <c r="BT400" t="n">
+        <v>178.4761904761905</v>
+      </c>
+      <c r="BU400" t="n">
+        <v>68.95238095238095</v>
+      </c>
+      <c r="BV400" t="inlineStr"/>
+      <c r="BW400" t="n">
+        <v>25.23809523809524</v>
+      </c>
+      <c r="BX400" t="n">
+        <v>181.5714285714286</v>
+      </c>
+      <c r="BY400" t="n">
+        <v>67.66666666666667</v>
+      </c>
+      <c r="BZ400" t="n">
+        <v>4904.761904761905</v>
+      </c>
+      <c r="CA400" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB400" t="n">
+        <v>188</v>
+      </c>
+      <c r="CC400" t="n">
+        <v>58</v>
+      </c>
+      <c r="CD400" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CE400" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF400" t="n">
+        <v>58</v>
+      </c>
+      <c r="CG400" t="inlineStr"/>
+      <c r="CH400" t="inlineStr"/>
+      <c r="CI400" t="inlineStr"/>
+      <c r="CJ400" t="inlineStr"/>
+      <c r="CK400" t="inlineStr"/>
+      <c r="CL400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>dYUosgsB</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="n">
+        <v>45553.85416666666</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F401" t="n">
+        <v>67795</v>
+      </c>
+      <c r="G401" t="n">
+        <v>2</v>
+      </c>
+      <c r="H401" t="n">
+        <v>2</v>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="K401" t="n">
+        <v>46</v>
+      </c>
+      <c r="L401" t="n">
+        <v>54</v>
+      </c>
+      <c r="M401" t="n">
+        <v>20</v>
+      </c>
+      <c r="N401" t="n">
+        <v>12</v>
+      </c>
+      <c r="O401" t="n">
+        <v>7</v>
+      </c>
+      <c r="P401" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>5</v>
+      </c>
+      <c r="R401" t="n">
+        <v>3</v>
+      </c>
+      <c r="S401" t="n">
+        <v>8</v>
+      </c>
+      <c r="T401" t="n">
+        <v>2</v>
+      </c>
+      <c r="U401" t="n">
+        <v>12</v>
+      </c>
+      <c r="V401" t="n">
+        <v>13</v>
+      </c>
+      <c r="W401" t="n">
+        <v>3</v>
+      </c>
+      <c r="X401" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA401" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB401" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC401" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD401" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF401" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG401" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH401" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI401" t="n">
+        <v>529</v>
+      </c>
+      <c r="AJ401" t="n">
+        <v>573</v>
+      </c>
+      <c r="AK401" t="n">
+        <v>449</v>
+      </c>
+      <c r="AL401" t="n">
+        <v>501</v>
+      </c>
+      <c r="AM401" t="n">
+        <v>124</v>
+      </c>
+      <c r="AN401" t="n">
+        <v>74</v>
+      </c>
+      <c r="AO401" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP401" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ401" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR401" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS401" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT401" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU401" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="AV401" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="AW401" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX401" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ401" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA401" t="inlineStr"/>
+      <c r="BB401" t="inlineStr"/>
+      <c r="BC401" t="inlineStr"/>
+      <c r="BD401" t="inlineStr"/>
+      <c r="BE401" t="inlineStr"/>
+      <c r="BF401" t="inlineStr"/>
+      <c r="BG401" t="inlineStr"/>
+      <c r="BH401" t="inlineStr"/>
+      <c r="BI401" t="inlineStr"/>
+      <c r="BJ401" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="BK401" t="n">
+        <v>29</v>
+      </c>
+      <c r="BL401" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="BM401" t="n">
+        <v>69</v>
+      </c>
+      <c r="BN401" t="n">
+        <v>8400</v>
+      </c>
+      <c r="BO401" t="n">
+        <v>24.18181818181818</v>
+      </c>
+      <c r="BP401" t="n">
+        <v>182.3636363636364</v>
+      </c>
+      <c r="BQ401" t="n">
+        <v>67.72727272727273</v>
+      </c>
+      <c r="BR401" t="inlineStr"/>
+      <c r="BS401" t="n">
+        <v>24.58823529411765</v>
+      </c>
+      <c r="BT401" t="n">
+        <v>178.1764705882353</v>
+      </c>
+      <c r="BU401" t="n">
+        <v>64.35294117647059</v>
+      </c>
+      <c r="BV401" t="inlineStr"/>
+      <c r="BW401" t="n">
+        <v>27.23809523809524</v>
+      </c>
+      <c r="BX401" t="n">
+        <v>182.5714285714286</v>
+      </c>
+      <c r="BY401" t="n">
+        <v>73.95238095238095</v>
+      </c>
+      <c r="BZ401" t="n">
+        <v>11380.95238095238</v>
+      </c>
+      <c r="CA401" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="CB401" t="n">
+        <v>176.6666666666667</v>
+      </c>
+      <c r="CC401" t="n">
+        <v>64.66666666666667</v>
+      </c>
+      <c r="CD401" t="inlineStr"/>
+      <c r="CE401" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF401" t="n">
+        <v>194</v>
+      </c>
+      <c r="CG401" t="n">
+        <v>24.83333333333333</v>
+      </c>
+      <c r="CH401" t="n">
+        <v>182</v>
+      </c>
+      <c r="CI401" t="n">
+        <v>73</v>
+      </c>
+      <c r="CJ401" t="n">
+        <v>7000</v>
+      </c>
+      <c r="CK401" t="n">
+        <v>6</v>
+      </c>
+      <c r="CL401" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>U3Cs29yR</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="n">
+        <v>45553.85416666666</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arreguin e 
+  usa </t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F402" t="n">
+        <v>18019</v>
+      </c>
+      <c r="G402" t="n">
+        <v>2</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="K402" t="n">
+        <v>59</v>
+      </c>
+      <c r="L402" t="n">
+        <v>41</v>
+      </c>
+      <c r="M402" t="n">
+        <v>21</v>
+      </c>
+      <c r="N402" t="n">
+        <v>15</v>
+      </c>
+      <c r="O402" t="n">
+        <v>9</v>
+      </c>
+      <c r="P402" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>5</v>
+      </c>
+      <c r="R402" t="n">
+        <v>4</v>
+      </c>
+      <c r="S402" t="n">
+        <v>7</v>
+      </c>
+      <c r="T402" t="n">
+        <v>4</v>
+      </c>
+      <c r="U402" t="n">
+        <v>15</v>
+      </c>
+      <c r="V402" t="n">
+        <v>13</v>
+      </c>
+      <c r="W402" t="n">
+        <v>8</v>
+      </c>
+      <c r="X402" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y402" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z402" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA402" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB402" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC402" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD402" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE402" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF402" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG402" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH402" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI402" t="n">
+        <v>538</v>
+      </c>
+      <c r="AJ402" t="n">
+        <v>423</v>
+      </c>
+      <c r="AK402" t="n">
+        <v>479</v>
+      </c>
+      <c r="AL402" t="n">
+        <v>345</v>
+      </c>
+      <c r="AM402" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN402" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO402" t="n">
+        <v>41</v>
+      </c>
+      <c r="AP402" t="n">
+        <v>31</v>
+      </c>
+      <c r="AQ402" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR402" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS402" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU402" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="AV402" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="AW402" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX402" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ402" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA402" t="inlineStr"/>
+      <c r="BB402" t="inlineStr"/>
+      <c r="BC402" t="inlineStr"/>
+      <c r="BD402" t="inlineStr"/>
+      <c r="BE402" t="inlineStr"/>
+      <c r="BF402" t="inlineStr"/>
+      <c r="BG402" t="inlineStr"/>
+      <c r="BH402" t="inlineStr"/>
+      <c r="BI402" t="inlineStr"/>
+      <c r="BJ402" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="BK402" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="BL402" t="n">
+        <v>179.2222222222222</v>
+      </c>
+      <c r="BM402" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="BN402" t="inlineStr"/>
+      <c r="BO402" t="n">
+        <v>22.11111111111111</v>
+      </c>
+      <c r="BP402" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BQ402" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="BR402" t="inlineStr"/>
+      <c r="BS402" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BT402" t="n">
+        <v>180.4444444444445</v>
+      </c>
+      <c r="BU402" t="n">
+        <v>67.22222222222223</v>
+      </c>
+      <c r="BV402" t="inlineStr"/>
+      <c r="BW402" t="n">
+        <v>23.19047619047619</v>
+      </c>
+      <c r="BX402" t="n">
+        <v>175.952380952381</v>
+      </c>
+      <c r="BY402" t="n">
+        <v>65.95238095238095</v>
+      </c>
+      <c r="BZ402" t="inlineStr"/>
+      <c r="CA402" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="CB402" t="n">
+        <v>180</v>
+      </c>
+      <c r="CC402" t="n">
+        <v>69.33333333333333</v>
+      </c>
+      <c r="CD402" t="n">
+        <v>4666.666666666667</v>
+      </c>
+      <c r="CE402" t="n">
+        <v>3</v>
+      </c>
+      <c r="CF402" t="n">
+        <v>208</v>
+      </c>
+      <c r="CG402" t="n">
+        <v>24</v>
+      </c>
+      <c r="CH402" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="CI402" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="CJ402" t="n">
+        <v>4500</v>
+      </c>
+      <c r="CK402" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL402" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>vcKjtDdH</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="n">
+        <v>45553.85416666666</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F403" t="n">
+        <v>19153</v>
+      </c>
+      <c r="G403" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" t="n">
+        <v>5</v>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="K403" t="n">
+        <v>62</v>
+      </c>
+      <c r="L403" t="n">
+        <v>38</v>
+      </c>
+      <c r="M403" t="n">
+        <v>27</v>
+      </c>
+      <c r="N403" t="n">
+        <v>12</v>
+      </c>
+      <c r="O403" t="n">
+        <v>10</v>
+      </c>
+      <c r="P403" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>8</v>
+      </c>
+      <c r="R403" t="n">
+        <v>2</v>
+      </c>
+      <c r="S403" t="n">
+        <v>9</v>
+      </c>
+      <c r="T403" t="n">
+        <v>3</v>
+      </c>
+      <c r="U403" t="n">
+        <v>13</v>
+      </c>
+      <c r="V403" t="n">
+        <v>20</v>
+      </c>
+      <c r="W403" t="n">
+        <v>12</v>
+      </c>
+      <c r="X403" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y403" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA403" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB403" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD403" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF403" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH403" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI403" t="n">
+        <v>661</v>
+      </c>
+      <c r="AJ403" t="n">
+        <v>366</v>
+      </c>
+      <c r="AK403" t="n">
+        <v>563</v>
+      </c>
+      <c r="AL403" t="n">
+        <v>284</v>
+      </c>
+      <c r="AM403" t="n">
+        <v>134</v>
+      </c>
+      <c r="AN403" t="n">
+        <v>71</v>
+      </c>
+      <c r="AO403" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP403" t="n">
+        <v>42</v>
+      </c>
+      <c r="AQ403" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR403" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS403" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT403" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU403" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="AV403" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="AW403" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX403" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ403" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA403" t="inlineStr"/>
+      <c r="BB403" t="inlineStr"/>
+      <c r="BC403" t="inlineStr"/>
+      <c r="BD403" t="inlineStr"/>
+      <c r="BE403" t="inlineStr"/>
+      <c r="BF403" t="inlineStr"/>
+      <c r="BG403" t="inlineStr"/>
+      <c r="BH403" t="inlineStr"/>
+      <c r="BI403" t="inlineStr"/>
+      <c r="BJ403" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="BK403" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="BL403" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="BM403" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="BN403" t="n">
+        <v>4625</v>
+      </c>
+      <c r="BO403" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BP403" t="n">
+        <v>181.5555555555555</v>
+      </c>
+      <c r="BQ403" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BR403" t="n">
+        <v>5666.666666666667</v>
+      </c>
+      <c r="BS403" t="n">
+        <v>22.65217391304348</v>
+      </c>
+      <c r="BT403" t="n">
+        <v>178.304347826087</v>
+      </c>
+      <c r="BU403" t="n">
+        <v>62.56521739130435</v>
+      </c>
+      <c r="BV403" t="inlineStr"/>
+      <c r="BW403" t="n">
+        <v>23.88235294117647</v>
+      </c>
+      <c r="BX403" t="n">
+        <v>183.7647058823529</v>
+      </c>
+      <c r="BY403" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ403" t="inlineStr"/>
+      <c r="CA403" t="n">
+        <v>22</v>
+      </c>
+      <c r="CB403" t="n">
+        <v>183</v>
+      </c>
+      <c r="CC403" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="CD403" t="inlineStr"/>
+      <c r="CE403" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF403" t="n">
+        <v>121</v>
+      </c>
+      <c r="CG403" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="CH403" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="CI403" t="n">
+        <v>69</v>
+      </c>
+      <c r="CJ403" t="inlineStr"/>
+      <c r="CK403" t="n">
+        <v>4</v>
+      </c>
+      <c r="CL403" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>Me49cTqr</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="n">
+        <v>45553.85416666666</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F404" t="n">
+        <v>21355</v>
+      </c>
+      <c r="G404" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="K404" t="n">
+        <v>50</v>
+      </c>
+      <c r="L404" t="n">
+        <v>50</v>
+      </c>
+      <c r="M404" t="n">
+        <v>10</v>
+      </c>
+      <c r="N404" t="n">
+        <v>7</v>
+      </c>
+      <c r="O404" t="n">
+        <v>3</v>
+      </c>
+      <c r="P404" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>2</v>
+      </c>
+      <c r="R404" t="n">
+        <v>2</v>
+      </c>
+      <c r="S404" t="n">
+        <v>5</v>
+      </c>
+      <c r="T404" t="n">
+        <v>1</v>
+      </c>
+      <c r="U404" t="n">
+        <v>20</v>
+      </c>
+      <c r="V404" t="n">
+        <v>12</v>
+      </c>
+      <c r="W404" t="n">
+        <v>1</v>
+      </c>
+      <c r="X404" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y404" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA404" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB404" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC404" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD404" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF404" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG404" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH404" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI404" t="n">
+        <v>562</v>
+      </c>
+      <c r="AJ404" t="n">
+        <v>557</v>
+      </c>
+      <c r="AK404" t="n">
+        <v>472</v>
+      </c>
+      <c r="AL404" t="n">
+        <v>482</v>
+      </c>
+      <c r="AM404" t="n">
+        <v>92</v>
+      </c>
+      <c r="AN404" t="n">
+        <v>87</v>
+      </c>
+      <c r="AO404" t="n">
+        <v>49</v>
+      </c>
+      <c r="AP404" t="n">
+        <v>42</v>
+      </c>
+      <c r="AQ404" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR404" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS404" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT404" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU404" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="AV404" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="AW404" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX404" t="n">
+        <v>1671</v>
+      </c>
+      <c r="AY404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ404" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA404" t="inlineStr"/>
+      <c r="BB404" t="inlineStr"/>
+      <c r="BC404" t="inlineStr"/>
+      <c r="BD404" t="inlineStr"/>
+      <c r="BE404" t="inlineStr"/>
+      <c r="BF404" t="inlineStr"/>
+      <c r="BG404" t="inlineStr"/>
+      <c r="BH404" t="inlineStr"/>
+      <c r="BI404" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="BJ404" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="BK404" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BL404" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="BM404" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="BN404" t="n">
+        <v>5100</v>
+      </c>
+      <c r="BO404" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="BP404" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="BQ404" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="BR404" t="n">
+        <v>3500</v>
+      </c>
+      <c r="BS404" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="BT404" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="BU404" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="BV404" t="inlineStr"/>
+      <c r="BW404" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="BX404" t="n">
+        <v>178.7142857142857</v>
+      </c>
+      <c r="BY404" t="n">
+        <v>67.52380952380952</v>
+      </c>
+      <c r="BZ404" t="n">
+        <v>4142.857142857143</v>
+      </c>
+      <c r="CA404" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="CB404" t="n">
+        <v>189</v>
+      </c>
+      <c r="CC404" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="CD404" t="n">
+        <v>5000</v>
+      </c>
+      <c r="CE404" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF404" t="n">
+        <v>133</v>
+      </c>
+      <c r="CG404" t="n">
+        <v>37</v>
+      </c>
+      <c r="CH404" t="n">
+        <v>186</v>
+      </c>
+      <c r="CI404" t="n">
+        <v>63</v>
+      </c>
+      <c r="CJ404" t="inlineStr"/>
+      <c r="CK404" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL404" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>SYdMjeTC</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="n">
+        <v>45553.91666666666</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dopka g 
+  usa </t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rio grande credit union field at isotopes park
+  albuquerque  nm </t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>13500</v>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="n">
+        <v>3</v>
+      </c>
+      <c r="H405" t="n">
+        <v>1</v>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="K405" t="n">
+        <v>48</v>
+      </c>
+      <c r="L405" t="n">
+        <v>52</v>
+      </c>
+      <c r="M405" t="n">
+        <v>14</v>
+      </c>
+      <c r="N405" t="n">
+        <v>16</v>
+      </c>
+      <c r="O405" t="n">
+        <v>8</v>
+      </c>
+      <c r="P405" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>3</v>
+      </c>
+      <c r="R405" t="n">
+        <v>5</v>
+      </c>
+      <c r="S405" t="n">
+        <v>3</v>
+      </c>
+      <c r="T405" t="n">
+        <v>5</v>
+      </c>
+      <c r="U405" t="inlineStr"/>
+      <c r="V405" t="inlineStr"/>
+      <c r="W405" t="n">
+        <v>4</v>
+      </c>
+      <c r="X405" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA405" t="inlineStr"/>
+      <c r="AB405" t="inlineStr"/>
+      <c r="AC405" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD405" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF405" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG405" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH405" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI405" t="n">
+        <v>428</v>
+      </c>
+      <c r="AJ405" t="n">
+        <v>457</v>
+      </c>
+      <c r="AK405" t="n">
+        <v>356</v>
+      </c>
+      <c r="AL405" t="n">
+        <v>367</v>
+      </c>
+      <c r="AM405" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN405" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO405" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP405" t="n">
+        <v>56</v>
+      </c>
+      <c r="AQ405" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR405" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT405" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU405" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="AV405" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="AW405" t="n">
+        <v>167</v>
+      </c>
+      <c r="AX405" t="n">
+        <v>1673</v>
+      </c>
+      <c r="AY405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ405" t="n">
+        <v>2024</v>
+      </c>
+      <c r="BA405" t="inlineStr"/>
+      <c r="BB405" t="inlineStr"/>
+      <c r="BC405" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD405" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE405" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF405" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG405" t="inlineStr"/>
+      <c r="BH405" t="inlineStr"/>
+      <c r="BI405" t="inlineStr"/>
+      <c r="BJ405" t="inlineStr"/>
+      <c r="BK405" t="inlineStr"/>
+      <c r="BL405" t="inlineStr"/>
+      <c r="BM405" t="inlineStr"/>
+      <c r="BN405" t="inlineStr"/>
+      <c r="BO405" t="inlineStr"/>
+      <c r="BP405" t="inlineStr"/>
+      <c r="BQ405" t="inlineStr"/>
+      <c r="BR405" t="inlineStr"/>
+      <c r="BS405" t="inlineStr"/>
+      <c r="BT405" t="inlineStr"/>
+      <c r="BU405" t="inlineStr"/>
+      <c r="BV405" t="inlineStr"/>
+      <c r="BW405" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX405" t="n">
+        <v>184</v>
+      </c>
+      <c r="BY405" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="BZ405" t="inlineStr"/>
+      <c r="CA405" t="inlineStr"/>
+      <c r="CB405" t="inlineStr"/>
+      <c r="CC405" t="inlineStr"/>
+      <c r="CD405" t="inlineStr"/>
+      <c r="CE405" t="inlineStr"/>
+      <c r="CF405" t="inlineStr"/>
+      <c r="CG405" t="inlineStr"/>
+      <c r="CH405" t="inlineStr"/>
+      <c r="CI405" t="inlineStr"/>
+      <c r="CJ405" t="inlineStr"/>
+      <c r="CK405" t="inlineStr"/>
+      <c r="CL405" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
